--- a/data/output/workbook/2026-07-11.xlsx
+++ b/data/output/workbook/2026-07-11.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 10:28</t>
+          <t>2026-07-11 12:03</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6507000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-186</v>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8980,17 +8980,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6331</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-129</v>
+        <v>-173</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9041,22 +9041,22 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5531</v>
+        <v>0.6224000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-124</v>
+        <v>-165</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9097,32 +9097,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5447</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-120</v>
+        <v>-127</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9163,32 +9163,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.437</v>
+        <v>0.5705</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>129</v>
+        <v>-133</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9244,17 +9244,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5447</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-125</v>
+        <v>-120</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9305,22 +9305,22 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5225</v>
+        <v>0.441</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-109</v>
+        <v>127</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9376,17 +9376,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5033</v>
+        <v>0.5557000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-101</v>
+        <v>-125</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5622</v>
+        <v>0.5317000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-128</v>
+        <v>-114</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9493,32 +9493,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5383</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-126</v>
+        <v>-117</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-103</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9559,32 +9559,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Portland Fire @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Portland Fire +14.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6361</v>
+        <v>0.5656</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-175</v>
+        <v>-130</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-138</v>
+        <v>105</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9625,12 +9625,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9644,13 +9644,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.4949</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-115</v>
+        <v>102</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9686,34 +9686,34 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4901</v>
+        <v>0.5051</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>122</v>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.5699000000000001</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-163</v>
+        <v>-133</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-133</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9823,12 +9823,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9838,17 +9838,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4781</v>
+        <v>0.6361</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>109</v>
+        <v>-175</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>127</v>
+        <v>-138</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9884,37 +9884,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +10.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.4901</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-115</v>
+        <v>104</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9950,37 +9950,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5734</v>
+        <v>0.5295</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-134</v>
+        <v>-113</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-113</v>
+        <v>105</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10031,22 +10031,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5067</v>
+        <v>0.4776</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-103</v>
+        <v>109</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 170</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.533</v>
+        <v>0.4218</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-114</v>
+        <v>137</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10153,32 +10153,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4967</v>
+        <v>0.509</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>101</v>
+        <v>-104</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10214,37 +10214,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4255</v>
+        <v>0.6195999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>135</v>
+        <v>-163</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>150</v>
+        <v>-138</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10280,37 +10280,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3818</v>
+        <v>0.4885</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10346,37 +10346,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Liberty @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 173.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5923</v>
+        <v>0.5049</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-145</v>
+        <v>-102</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-127</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10427,22 +10427,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5118</v>
+        <v>0.4705</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-105</v>
+        <v>113</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 47.1% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3690861999999995</v>
+        <v>0.3587399999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>113</v>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6309138000000005</v>
+        <v>0.6412600000000001</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-171</v>
+        <v>-179</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10775,10 +10775,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4775</v>
+        <v>0.4683</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>105</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5225</v>
+        <v>0.5317000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-109</v>
+        <v>-114</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>122</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.437</v>
+        <v>0.441</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-129</v>
+        <v>-127</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11111,7 +11111,7 @@
         <v>-120</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5295</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>105</v>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.4705</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>122</v>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.1% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3493</v>
+        <v>0.3499</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>186</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6507000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-186</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11441,7 +11441,7 @@
         <v>286</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11567,13 +11567,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5033</v>
+        <v>0.4949</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>102</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4967</v>
+        <v>0.5051</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>-102</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11699,13 +11699,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4648</v>
+        <v>0.4583</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11765,13 +11765,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5352</v>
+        <v>0.5417000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11831,13 +11831,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4489288</v>
+        <v>0.452091</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5510712</v>
+        <v>0.547909</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11959,17 +11959,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.5705</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>111</v>
+        <v>-133</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12025,17 +12025,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4384000000000001</v>
+        <v>0.4295</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12091,17 +12091,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6161</v>
+        <v>0.3669</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-160</v>
+        <v>173</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-153</v>
+        <v>162</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 36.7% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12157,17 +12157,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3839</v>
+        <v>0.6331</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>160</v>
+        <v>-173</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4317</v>
+        <v>0.4326</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5683</v>
+        <v>0.5674</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12359,13 +12359,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5326</v>
+        <v>0.5533</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-114</v>
+        <v>-124</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12425,13 +12425,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4674</v>
+        <v>0.4467</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3875</v>
+        <v>0.3906</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12557,13 +12557,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6125</v>
+        <v>0.6093999999999999</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-158</v>
+        <v>-156</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.523841</v>
+        <v>0.53142</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>105</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4761589999999999</v>
+        <v>0.46858</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>178</v>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4436</v>
+        <v>0.4443</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>125</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5557000000000001</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-125</v>
@@ -12887,13 +12887,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5118</v>
+        <v>0.509</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4882</v>
+        <v>0.491</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-108</v>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13019,13 +13019,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.421</v>
+        <v>0.4209000000000001</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>138</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.579</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>-138</v>
@@ -13147,17 +13147,17 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3631</v>
+        <v>0.4617</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13213,17 +13213,17 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5531</v>
+        <v>0.5383</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-124</v>
+        <v>-117</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13283,13 +13283,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3935</v>
+        <v>0.3776</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6065</v>
+        <v>0.6224000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-154</v>
+        <v>-165</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-153</v>
+        <v>162</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4812</v>
+        <v>0.4797</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>108</v>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13481,13 +13481,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5188</v>
+        <v>0.5203</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13553,7 +13553,7 @@
         <v>-120</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.511</v>
+        <v>0.5103</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>-104</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4007</v>
+        <v>0.4014</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>106</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14075,13 +14075,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4255</v>
+        <v>0.4218</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5745</v>
+        <v>0.5782</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-135</v>
+        <v>-137</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-156</v>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5219</v>
+        <v>0.5224</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-109</v>
@@ -14273,7 +14273,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4781</v>
+        <v>0.4776</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>109</v>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5067</v>
+        <v>0.4885</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14401,17 +14401,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4933</v>
+        <v>0.4191000000000001</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-112</v>
+        <v>100</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.596</v>
+        <v>0.5914</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-148</v>
+        <v>-145</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-141</v>
+        <v>-138</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14537,13 +14537,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.404</v>
+        <v>0.4086</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4547</v>
+        <v>0.4539</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>120</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14667,7 +14667,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5453</v>
+        <v>0.5461</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>-120</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15371,10 +15371,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5266</v>
+        <v>0.5278</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>-117</v>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15437,10 +15437,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4734</v>
+        <v>0.4722</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>113</v>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15767,13 +15767,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5734</v>
+        <v>0.5699000000000001</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15833,10 +15833,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4266</v>
+        <v>0.4301</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>117</v>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16295,10 +16295,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4077</v>
+        <v>0.3587399999999999</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>133</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,13 +16361,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5923</v>
+        <v>0.6412600000000001</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-145</v>
+        <v>-179</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.4728</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H101" s="15" t="n"/>
       <c r="I101" s="13">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17011,10 +17011,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5272</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="13">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17478,7 +17478,7 @@
         <v>204</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -17544,7 +17544,7 @@
         <v>-204</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -17604,13 +17604,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4878</v>
+        <v>0.4951</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -17670,13 +17670,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5049</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -17700,7 +17700,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -17732,17 +17732,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -6.5</t>
+          <t>Minnesota Lynx -7.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4849254556076258</v>
+        <v>0.4536141029303052</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -17798,17 +17798,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty +6.5</t>
+          <t>New York Liberty +7.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5150745443923742</v>
+        <v>0.5463858970696948</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-106</v>
+        <v>-120</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -17874,7 +17874,7 @@
         <v>341</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>614</v>
+        <v>700</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17940,7 +17940,7 @@
         <v>-341</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -17996,17 +17996,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 174.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5622</v>
+        <v>0.5870644226482148</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-128</v>
+        <v>-142</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -18062,17 +18062,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 173.5</t>
+          <t>Under 174.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4378</v>
+        <v>0.4129355773517852</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -18128,17 +18128,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -13.5</t>
+          <t>Atlanta Dream -14.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.442</v>
+        <v>0.4344</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -18194,17 +18194,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Portland Fire +14.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5656</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -18392,17 +18392,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 170</t>
+          <t>Over 171</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5556700048059063</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>-125</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -18458,14 +18458,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 170</t>
+          <t>Under 171</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.444</v>
+        <v>0.4211299951940937</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -18492,7 +18492,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -18524,17 +18524,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -10.5</t>
+          <t>Las Vegas Aces -10</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4644</v>
+        <v>0.4626</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -18590,17 +18590,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +10.5</t>
+          <t>Phoenix Mercury +10</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.5063</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-115</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -18660,13 +18660,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.6195999999999999</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-163</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -18726,13 +18726,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3796</v>
+        <v>0.3804</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>163</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3859</v>
+        <v>0.3875999999999999</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>156</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6141</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-159</v>
+        <v>-158</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -18924,13 +18924,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.242</v>
+        <v>0.2307</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 24.2% (fair +313). Your call.</t>
+          <t>Model 23.1% (fair +333). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -18990,10 +18990,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.758</v>
+        <v>0.7693</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-313</v>
+        <v>-333</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-300</v>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 75.8% (fair -313). Your call.</t>
+          <t>Model 76.9% (fair -333). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -19056,13 +19056,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3818</v>
+        <v>0.3901</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6182</v>
+        <v>0.6099</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>

--- a/data/output/workbook/2026-07-11.xlsx
+++ b/data/output/workbook/2026-07-11.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10534650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 12:03</t>
+          <t>2026-07-11 14:02</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4915,171 +4915,250 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs New York Mets defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.862</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.275</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.2</v>
+        <v>8.304</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.862</v>
+        <v>7.918</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.304</v>
+        <v>0.739</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -5143,22 +5222,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.918</v>
+        <v>0.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.739</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5222,313 +5301,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.918</v>
+        <v>9.061</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.239000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.392</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.8</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.061</v>
+        <v>0.542</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Boston Red Sox defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.069</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.069</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
+        <v>7.306</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.467</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.013</v>
+        <v>8.391</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.306</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -5592,22 +5671,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.391</v>
+        <v>1.217</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5671,151 +5750,72 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.217</v>
+        <v>8.587</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.542</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.367</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.587</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7694,7 +7694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7711,167 +7711,246 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Detroit Tigers defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Detroit Tigers defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.447</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.447</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>7.234</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.267</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>3.852</v>
+        <v>7.592</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.234</v>
+        <v>1.213</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7935,22 +8014,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.592</v>
+        <v>0.898</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.213</v>
+        <v>8.426</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -8014,317 +8093,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.898</v>
+        <v>7.776</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.537</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.167</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>7.776</v>
+        <v>0.333</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Detroit Tigers offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Detroit Tigers offense vs Philadelphia Phillies defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.906</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.033</v>
+        <v>7.755</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.906</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.755</v>
+        <v>1.02</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -8388,22 +8467,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>9.319000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.02</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -8467,151 +8546,72 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.17</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6703</v>
+        <v>0.6698999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-203</v>
@@ -8984,13 +8984,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6331</v>
+        <v>0.633</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-173</v>
+        <v>-172</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9026,17 +9026,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6224000000000001</v>
+        <v>0.6566000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-165</v>
+        <v>-191</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 65.7% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9112,17 +9112,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.6089</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-127</v>
+        <v>-156</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9163,32 +9163,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5705</v>
+        <v>0.5576</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-133</v>
+        <v>-126</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5447</v>
+        <v>0.5554</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>127</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.441</v>
+        <v>0.4424</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>178</v>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9380,13 +9380,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5557000000000001</v>
+        <v>0.5424</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-125</v>
+        <v>-119</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 54.2% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9442,14 +9442,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5317000000000001</v>
+        <v>0.5295</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>122</v>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5383</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-117</v>
+        <v>-112</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9578,13 +9578,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5656</v>
+        <v>0.5686</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9625,12 +9625,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4949</v>
+        <v>0.5509000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>102</v>
+        <v>-123</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Portland Fire @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9706,17 +9706,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 174.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5051</v>
+        <v>0.5362</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-102</v>
+        <v>-116</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9752,37 +9752,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5699000000000001</v>
+        <v>0.5051</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>-102</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>120</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9823,32 +9823,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6361</v>
+        <v>0.4949</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-175</v>
+        <v>102</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-138</v>
+        <v>122</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9889,12 +9889,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4901</v>
+        <v>0.5699000000000001</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104</v>
+        <v>-133</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9955,12 +9955,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9970,17 +9970,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5295</v>
+        <v>0.5275</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -113). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10021,12 +10021,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10036,17 +10036,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4776</v>
+        <v>0.6429</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>109</v>
+        <v>-180</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 64.3% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4218</v>
+        <v>0.4765</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10148,7 +10148,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -10158,27 +10158,27 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.509</v>
+        <v>0.487</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-104</v>
+        <v>105</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10214,37 +10214,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6195999999999999</v>
+        <v>0.4371</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-163</v>
+        <v>129</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-138</v>
+        <v>147</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Phoenix Mercury +10.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4885</v>
+        <v>0.5375</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>105</v>
+        <v>-116</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10351,12 +10351,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Minnesota Lynx</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10366,17 +10366,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 173.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5049</v>
+        <v>0.4919</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10412,7 +10412,7 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -10432,17 +10432,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4705</v>
+        <v>0.5589</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>113</v>
+        <v>-127</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>-110</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +113). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10499,7 +10499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3587399999999999</v>
+        <v>0.3630001999999994</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>113</v>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6412600000000001</v>
+        <v>0.6369998000000006</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-179</v>
+        <v>-175</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10775,13 +10775,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4683</v>
+        <v>0.4713</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5317000000000001</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>122</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.441</v>
+        <v>0.4424</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.5576</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11111,7 +11111,7 @@
         <v>-120</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11177,7 +11177,7 @@
         <v>-113</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11441,7 +11441,7 @@
         <v>286</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11573,7 +11573,7 @@
         <v>102</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11639,7 +11639,7 @@
         <v>-102</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4583</v>
+        <v>0.4572</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>122</v>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11765,13 +11765,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5417000000000001</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11831,13 +11831,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.452091</v>
+        <v>0.4509795</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.547909</v>
+        <v>0.5490205</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11959,14 +11959,14 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5705</v>
+        <v>0.4658</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-133</v>
+        <v>115</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12025,17 +12025,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4295</v>
+        <v>0.447</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12095,13 +12095,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3669</v>
+        <v>0.367</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +173). Your call.</t>
+          <t>Model 36.7% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12161,13 +12161,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6331</v>
+        <v>0.633</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-173</v>
+        <v>-172</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4326</v>
+        <v>0.423</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5674</v>
+        <v>0.577</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-131</v>
+        <v>-136</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12355,17 +12355,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5533</v>
+        <v>0.4666</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-124</v>
+        <v>114</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-113</v>
+        <v>110</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12421,17 +12421,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4467</v>
+        <v>0.4462</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>124</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3906</v>
+        <v>0.3987</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12557,13 +12557,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6093999999999999</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-156</v>
+        <v>-151</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.53142</v>
+        <v>0.53285</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>105</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12689,13 +12689,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.46858</v>
+        <v>0.46715</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4443</v>
+        <v>0.4576</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>122</v>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 45.8% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12821,13 +12821,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5557000000000001</v>
+        <v>0.5424</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-125</v>
+        <v>-119</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 54.2% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12887,13 +12887,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.509</v>
+        <v>0.502</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12953,13 +12953,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.491</v>
+        <v>0.498</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13019,13 +13019,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4209000000000001</v>
+        <v>0.419</v>
       </c>
       <c r="G41" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="H41" s="15" t="n">
         <v>138</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>141</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13085,13 +13085,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-144</v>
+        <v>-140</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13147,14 +13147,14 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4617</v>
+        <v>0.3651</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>117</v>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13213,17 +13213,17 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5383</v>
+        <v>0.5509000000000001</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13283,13 +13283,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3776</v>
+        <v>0.3911</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6224000000000001</v>
+        <v>0.6089</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-165</v>
+        <v>-156</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4797</v>
+        <v>0.4807</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>108</v>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13481,13 +13481,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5203</v>
+        <v>0.5193</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5447</v>
+        <v>0.5554</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>127</v>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13613,13 +13613,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4553</v>
+        <v>0.4446</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3297</v>
+        <v>0.3301</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>203</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6703</v>
+        <v>0.6698999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>-203</v>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3639</v>
+        <v>0.3571</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 35.7% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6361</v>
+        <v>0.6429</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-175</v>
+        <v>-180</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 64.3% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5103</v>
+        <v>0.509</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>-104</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,13 +14009,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4014</v>
+        <v>0.4025</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.2% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14075,13 +14075,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4218</v>
+        <v>0.4371</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14141,13 +14141,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5782</v>
+        <v>0.5629</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-137</v>
+        <v>-129</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14207,13 +14207,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5224</v>
+        <v>0.5235000000000001</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-127</v>
+        <v>-130</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14237,7 +14237,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14273,10 +14273,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4776</v>
+        <v>0.4765</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>127</v>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4885</v>
+        <v>0.4919</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4191000000000001</v>
+        <v>0.4157</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>100</v>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 41.6% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5914</v>
+        <v>0.5907</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14537,10 +14537,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4086</v>
+        <v>0.4093</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>133</v>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4539</v>
+        <v>0.4547</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>120</v>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14667,7 +14667,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5461</v>
+        <v>0.5453</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>-120</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5278</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-112</v>
+        <v>-109</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15437,13 +15437,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4722</v>
+        <v>0.4783</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15484,32 +15484,32 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.429</v>
+        <v>0.5589</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>133</v>
+        <v>-127</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>133</v>
+        <v>-110</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15550,32 +15550,32 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 6.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.571</v>
+        <v>0.4411</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-133</v>
+        <v>127</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15616,32 +15616,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5099</v>
+        <v>0.6036</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-104</v>
+        <v>-152</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-117</v>
+        <v>-180</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4901</v>
+        <v>0.3964</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 39.6% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15748,12 +15748,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15763,17 +15763,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5699000000000001</v>
+        <v>0.429</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-133</v>
+        <v>133</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-108</v>
+        <v>133</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15814,12 +15814,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15829,17 +15829,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4301</v>
+        <v>0.571</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>133</v>
+        <v>-133</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>117</v>
+        <v>-127</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15880,32 +15880,32 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4574</v>
+        <v>0.4789</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15946,32 +15946,32 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5426</v>
+        <v>0.5211</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-119</v>
+        <v>-109</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16012,32 +16012,32 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4346</v>
+        <v>0.3987</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16078,32 +16078,32 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5654</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-130</v>
+        <v>-151</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-133</v>
+        <v>-170</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16144,12 +16144,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.513</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>107</v>
+        <v>-105</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16210,12 +16210,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.487</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-107</v>
+        <v>105</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -16291,17 +16291,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3587399999999999</v>
+        <v>0.5699000000000001</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>179</v>
+        <v>-133</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>133</v>
+        <v>-108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
@@ -16357,17 +16357,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.6412600000000001</v>
+        <v>0.4301</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-179</v>
+        <v>133</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16408,32 +16408,32 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.416</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>140</v>
+        <v>-112</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>144</v>
+        <v>-110</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16474,32 +16474,32 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.584</v>
+        <v>0.4723000000000001</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-140</v>
+        <v>112</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-138</v>
+        <v>-110</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16540,32 +16540,32 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.453828</v>
+        <v>0.5303</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>120</v>
+        <v>-113</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>113</v>
+        <v>-145</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16606,32 +16606,32 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.546172</v>
+        <v>0.4697</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-120</v>
+        <v>113</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16672,12 +16672,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -16687,16 +16687,18 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.3964</v>
+        <v>0.4574</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>152</v>
-      </c>
-      <c r="H97" s="15" t="n"/>
+        <v>119</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>117</v>
+      </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
         <v/>
@@ -16719,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +152). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16736,12 +16738,12 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -16751,16 +16753,18 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.6036</v>
+        <v>0.5426</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-152</v>
-      </c>
-      <c r="H98" s="15" t="n"/>
+        <v>-119</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>-117</v>
+      </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
         <v/>
@@ -16783,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -152). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16800,31 +16804,33 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4529</v>
+        <v>0.4931</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="H99" s="15" t="n"/>
+        <v>103</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>-115</v>
+      </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
         <v/>
@@ -16847,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16864,31 +16870,33 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5471</v>
+        <v>0.5069</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H100" s="15" t="n"/>
+        <v>-103</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
         <v/>
@@ -16911,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16928,12 +16936,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -16943,16 +16951,18 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4728</v>
+        <v>0.4453</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>112</v>
-      </c>
-      <c r="H101" s="15" t="n"/>
+        <v>125</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>127</v>
+      </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
         <v/>
@@ -16975,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16992,12 +17002,12 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -17007,16 +17017,18 @@
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5272</v>
+        <v>0.5547</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H102" s="15" t="n"/>
+        <v>-125</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>-127</v>
+      </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
         <v/>
@@ -17039,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17056,31 +17068,33 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.3872</v>
+        <v>0.5221</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>158</v>
-      </c>
-      <c r="H103" s="15" t="n"/>
+        <v>-109</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>-115</v>
+      </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
         <v/>
@@ -17103,7 +17117,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17120,31 +17134,33 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.6128</v>
+        <v>0.4779</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H104" s="15" t="n"/>
+        <v>109</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
         <v/>
@@ -17167,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17184,31 +17200,33 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.3434</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H105" s="15" t="n"/>
+        <v>191</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>155</v>
+      </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
         <v/>
@@ -17231,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 34.3% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17248,31 +17266,33 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.6566000000000001</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="H106" s="15" t="n"/>
+        <v>-191</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>155</v>
+      </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
         <v/>
@@ -17295,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 65.7% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17304,9 +17324,2761 @@
         <v/>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.4% (fair +107). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.5163</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.6% (fair -107). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Over 7.5</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.5% (fair -115). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Under 7.5</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.5% (fair +115). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers +1.5</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.2% (fair -172). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies -1.5</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>172</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.8% (fair +172). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Miami Marlins</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.3587399999999999</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>179</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.9% (fair +179). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Miami Marlins</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.6412600000000001</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>-179</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.1% (fair -179). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>144</v>
+      </c>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.6% (fair +140). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-138</v>
+      </c>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.4% (fair -140). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.3% (fair -119). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.4572000000000001</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.7% (fair +119). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Twins -1.5</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>143</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.2% (fair +143). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels +1.5</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.5884</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>-143</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-165</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.8% (fair -143). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>0.453828</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I121" s="13">
+        <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
+        <v/>
+      </c>
+      <c r="J121" s="16">
+        <f>IF($H$121="","",$F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF($H$121="","",MAX(0,($F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))/IF($H$121&lt;0,-100/$H$121,$H$121/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L121" s="18">
+        <f>IF($H$121="","",ROUND(MIN($K$121,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M121" s="12">
+        <f>IF($J$121="","",IF($J$121&lt;0,"Pass",IF($J$121&lt;'Settings'!$B$4,"Thin",IF($J$121&lt;0.06,"✅ Sharp band",IF($J$121&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N121" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.4% (fair +120). Your call.</t>
+        </is>
+      </c>
+      <c r="O121" s="15" t="n"/>
+      <c r="P121" s="16">
+        <f>IF(OR($H$121="",$O$121=""),"",(1+IF($H$121&lt;0,-100/$H$121,$H$121/100))/(1+IF($O$121&lt;0,-100/$O$121,$O$121/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0.546172</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I122" s="13">
+        <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
+        <v/>
+      </c>
+      <c r="J122" s="16">
+        <f>IF($H$122="","",$F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))</f>
+        <v/>
+      </c>
+      <c r="K122" s="17">
+        <f>IF($H$122="","",MAX(0,($F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))/IF($H$122&lt;0,-100/$H$122,$H$122/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L122" s="18">
+        <f>IF($H$122="","",ROUND(MIN($K$122,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M122" s="12">
+        <f>IF($J$122="","",IF($J$122&lt;0,"Pass",IF($J$122&lt;'Settings'!$B$4,"Thin",IF($J$122&lt;0.06,"✅ Sharp band",IF($J$122&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N122" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.6% (fair -120). Your call.</t>
+        </is>
+      </c>
+      <c r="O122" s="15" t="n"/>
+      <c r="P122" s="16">
+        <f>IF(OR($H$122="",$O$122=""),"",(1+IF($H$122&lt;0,-100/$H$122,$H$122/100))/(1+IF($O$122&lt;0,-100/$O$122,$O$122/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I123" s="13">
+        <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
+        <v/>
+      </c>
+      <c r="J123" s="16">
+        <f>IF($H$123="","",$F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))</f>
+        <v/>
+      </c>
+      <c r="K123" s="17">
+        <f>IF($H$123="","",MAX(0,($F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))/IF($H$123&lt;0,-100/$H$123,$H$123/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L123" s="18">
+        <f>IF($H$123="","",ROUND(MIN($K$123,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M123" s="12">
+        <f>IF($J$123="","",IF($J$123&lt;0,"Pass",IF($J$123&lt;'Settings'!$B$4,"Thin",IF($J$123&lt;0.06,"✅ Sharp band",IF($J$123&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N123" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.5% (fair -125). Your call.</t>
+        </is>
+      </c>
+      <c r="O123" s="15" t="n"/>
+      <c r="P123" s="16">
+        <f>IF(OR($H$123="",$O$123=""),"",(1+IF($H$123&lt;0,-100/$H$123,$H$123/100))/(1+IF($O$123&lt;0,-100/$O$123,$O$123/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I124" s="13">
+        <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
+        <v/>
+      </c>
+      <c r="J124" s="16">
+        <f>IF($H$124="","",$F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))</f>
+        <v/>
+      </c>
+      <c r="K124" s="17">
+        <f>IF($H$124="","",MAX(0,($F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))/IF($H$124&lt;0,-100/$H$124,$H$124/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L124" s="18">
+        <f>IF($H$124="","",ROUND(MIN($K$124,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M124" s="12">
+        <f>IF($J$124="","",IF($J$124&lt;0,"Pass",IF($J$124&lt;'Settings'!$B$4,"Thin",IF($J$124&lt;0.06,"✅ Sharp band",IF($J$124&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N124" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.5% (fair +125). Your call.</t>
+        </is>
+      </c>
+      <c r="O124" s="15" t="n"/>
+      <c r="P124" s="16">
+        <f>IF(OR($H$124="",$O$124=""),"",(1+IF($H$124&lt;0,-100/$H$124,$H$124/100))/(1+IF($O$124&lt;0,-100/$O$124,$O$124/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox +1.5</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>-160</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I125" s="13">
+        <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
+        <v/>
+      </c>
+      <c r="J125" s="16">
+        <f>IF($H$125="","",$F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))</f>
+        <v/>
+      </c>
+      <c r="K125" s="17">
+        <f>IF($H$125="","",MAX(0,($F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))/IF($H$125&lt;0,-100/$H$125,$H$125/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L125" s="18">
+        <f>IF($H$125="","",ROUND(MIN($K$125,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M125" s="12">
+        <f>IF($J$125="","",IF($J$125&lt;0,"Pass",IF($J$125&lt;'Settings'!$B$4,"Thin",IF($J$125&lt;0.06,"✅ Sharp band",IF($J$125&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N125" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.5% (fair -160). Your call.</t>
+        </is>
+      </c>
+      <c r="O125" s="15" t="n"/>
+      <c r="P125" s="16">
+        <f>IF(OR($H$125="",$O$125=""),"",(1+IF($H$125&lt;0,-100/$H$125,$H$125/100))/(1+IF($O$125&lt;0,-100/$O$125,$O$125/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>Athletics @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>Athletics -1.5</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="I126" s="13">
+        <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
+        <v/>
+      </c>
+      <c r="J126" s="16">
+        <f>IF($H$126="","",$F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))</f>
+        <v/>
+      </c>
+      <c r="K126" s="17">
+        <f>IF($H$126="","",MAX(0,($F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))/IF($H$126&lt;0,-100/$H$126,$H$126/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L126" s="18">
+        <f>IF($H$126="","",ROUND(MIN($K$126,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M126" s="12">
+        <f>IF($J$126="","",IF($J$126&lt;0,"Pass",IF($J$126&lt;'Settings'!$B$4,"Thin",IF($J$126&lt;0.06,"✅ Sharp band",IF($J$126&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N126" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.5% (fair +160). Your call.</t>
+        </is>
+      </c>
+      <c r="O126" s="15" t="n"/>
+      <c r="P126" s="16">
+        <f>IF(OR($H$126="",$O$126=""),"",(1+IF($H$126&lt;0,-100/$H$126,$H$126/100))/(1+IF($O$126&lt;0,-100/$O$126,$O$126/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>155</v>
+      </c>
+      <c r="H127" s="15" t="n"/>
+      <c r="I127" s="13">
+        <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>IF($H$127="","",$F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))</f>
+        <v/>
+      </c>
+      <c r="K127" s="17">
+        <f>IF($H$127="","",MAX(0,($F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))/IF($H$127&lt;0,-100/$H$127,$H$127/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L127" s="18">
+        <f>IF($H$127="","",ROUND(MIN($K$127,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M127" s="12">
+        <f>IF($J$127="","",IF($J$127&lt;0,"Pass",IF($J$127&lt;'Settings'!$B$4,"Thin",IF($J$127&lt;0.06,"✅ Sharp band",IF($J$127&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N127" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.2% (fair +155). Your call.</t>
+        </is>
+      </c>
+      <c r="O127" s="15" t="n"/>
+      <c r="P127" s="16">
+        <f>IF(OR($H$127="",$O$127=""),"",(1+IF($H$127&lt;0,-100/$H$127,$H$127/100))/(1+IF($O$127&lt;0,-100/$O$127,$O$127/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>0.6082</v>
+      </c>
+      <c r="G128" s="14" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="13">
+        <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
+        <v/>
+      </c>
+      <c r="J128" s="16">
+        <f>IF($H$128="","",$F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))</f>
+        <v/>
+      </c>
+      <c r="K128" s="17">
+        <f>IF($H$128="","",MAX(0,($F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))/IF($H$128&lt;0,-100/$H$128,$H$128/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L128" s="18">
+        <f>IF($H$128="","",ROUND(MIN($K$128,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M128" s="12">
+        <f>IF($J$128="","",IF($J$128&lt;0,"Pass",IF($J$128&lt;'Settings'!$B$4,"Thin",IF($J$128&lt;0.06,"✅ Sharp band",IF($J$128&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N128" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.8% (fair -155). Your call.</t>
+        </is>
+      </c>
+      <c r="O128" s="15" t="n"/>
+      <c r="P128" s="16">
+        <f>IF(OR($H$128="",$O$128=""),"",(1+IF($H$128&lt;0,-100/$H$128,$H$128/100))/(1+IF($O$128&lt;0,-100/$O$128,$O$128/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Over 9.5</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I129" s="13">
+        <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
+        <v/>
+      </c>
+      <c r="J129" s="16">
+        <f>IF($H$129="","",$F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))</f>
+        <v/>
+      </c>
+      <c r="K129" s="17">
+        <f>IF($H$129="","",MAX(0,($F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))/IF($H$129&lt;0,-100/$H$129,$H$129/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L129" s="18">
+        <f>IF($H$129="","",ROUND(MIN($K$129,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M129" s="12">
+        <f>IF($J$129="","",IF($J$129&lt;0,"Pass",IF($J$129&lt;'Settings'!$B$4,"Thin",IF($J$129&lt;0.06,"✅ Sharp band",IF($J$129&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N129" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.2% (fair +121). Your call.</t>
+        </is>
+      </c>
+      <c r="O129" s="15" t="n"/>
+      <c r="P129" s="16">
+        <f>IF(OR($H$129="",$O$129=""),"",(1+IF($H$129&lt;0,-100/$H$129,$H$129/100))/(1+IF($O$129&lt;0,-100/$O$129,$O$129/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="G130" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I130" s="13">
+        <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
+        <v/>
+      </c>
+      <c r="J130" s="16">
+        <f>IF($H$130="","",$F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))</f>
+        <v/>
+      </c>
+      <c r="K130" s="17">
+        <f>IF($H$130="","",MAX(0,($F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))/IF($H$130&lt;0,-100/$H$130,$H$130/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L130" s="18">
+        <f>IF($H$130="","",ROUND(MIN($K$130,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M130" s="12">
+        <f>IF($J$130="","",IF($J$130&lt;0,"Pass",IF($J$130&lt;'Settings'!$B$4,"Thin",IF($J$130&lt;0.06,"✅ Sharp band",IF($J$130&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N130" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.8% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O130" s="15" t="n"/>
+      <c r="P130" s="16">
+        <f>IF(OR($H$130="",$O$130=""),"",(1+IF($H$130&lt;0,-100/$H$130,$H$130/100))/(1+IF($O$130&lt;0,-100/$O$130,$O$130/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals -1.5</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>138</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="I131" s="13">
+        <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
+        <v/>
+      </c>
+      <c r="J131" s="16">
+        <f>IF($H$131="","",$F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))</f>
+        <v/>
+      </c>
+      <c r="K131" s="17">
+        <f>IF($H$131="","",MAX(0,($F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))/IF($H$131&lt;0,-100/$H$131,$H$131/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L131" s="18">
+        <f>IF($H$131="","",ROUND(MIN($K$131,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M131" s="12">
+        <f>IF($J$131="","",IF($J$131&lt;0,"Pass",IF($J$131&lt;'Settings'!$B$4,"Thin",IF($J$131&lt;0.06,"✅ Sharp band",IF($J$131&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N131" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.9% (fair +138). Your call.</t>
+        </is>
+      </c>
+      <c r="O131" s="15" t="n"/>
+      <c r="P131" s="16">
+        <f>IF(OR($H$131="",$O$131=""),"",(1+IF($H$131&lt;0,-100/$H$131,$H$131/100))/(1+IF($O$131&lt;0,-100/$O$131,$O$131/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves +1.5</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="G132" s="14" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I132" s="13">
+        <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>IF($H$132="","",$F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))</f>
+        <v/>
+      </c>
+      <c r="K132" s="17">
+        <f>IF($H$132="","",MAX(0,($F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))/IF($H$132&lt;0,-100/$H$132,$H$132/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L132" s="18">
+        <f>IF($H$132="","",ROUND(MIN($K$132,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M132" s="12">
+        <f>IF($J$132="","",IF($J$132&lt;0,"Pass",IF($J$132&lt;'Settings'!$B$4,"Thin",IF($J$132&lt;0.06,"✅ Sharp band",IF($J$132&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N132" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.1% (fair -138). Your call.</t>
+        </is>
+      </c>
+      <c r="O132" s="15" t="n"/>
+      <c r="P132" s="16">
+        <f>IF(OR($H$132="",$O$132=""),"",(1+IF($H$132&lt;0,-100/$H$132,$H$132/100))/(1+IF($O$132&lt;0,-100/$O$132,$O$132/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="G133" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="13">
+        <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
+        <v/>
+      </c>
+      <c r="J133" s="16">
+        <f>IF($H$133="","",$F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))</f>
+        <v/>
+      </c>
+      <c r="K133" s="17">
+        <f>IF($H$133="","",MAX(0,($F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))/IF($H$133&lt;0,-100/$H$133,$H$133/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L133" s="18">
+        <f>IF($H$133="","",ROUND(MIN($K$133,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M133" s="12">
+        <f>IF($J$133="","",IF($J$133&lt;0,"Pass",IF($J$133&lt;'Settings'!$B$4,"Thin",IF($J$133&lt;0.06,"✅ Sharp band",IF($J$133&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N133" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.3% (fair +121). Your call.</t>
+        </is>
+      </c>
+      <c r="O133" s="15" t="n"/>
+      <c r="P133" s="16">
+        <f>IF(OR($H$133="",$O$133=""),"",(1+IF($H$133&lt;0,-100/$H$133,$H$133/100))/(1+IF($O$133&lt;0,-100/$O$133,$O$133/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="G134" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="13">
+        <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
+        <v/>
+      </c>
+      <c r="J134" s="16">
+        <f>IF($H$134="","",$F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))</f>
+        <v/>
+      </c>
+      <c r="K134" s="17">
+        <f>IF($H$134="","",MAX(0,($F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))/IF($H$134&lt;0,-100/$H$134,$H$134/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L134" s="18">
+        <f>IF($H$134="","",ROUND(MIN($K$134,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M134" s="12">
+        <f>IF($J$134="","",IF($J$134&lt;0,"Pass",IF($J$134&lt;'Settings'!$B$4,"Thin",IF($J$134&lt;0.06,"✅ Sharp band",IF($J$134&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N134" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.7% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O134" s="15" t="n"/>
+      <c r="P134" s="16">
+        <f>IF(OR($H$134="",$O$134=""),"",(1+IF($H$134&lt;0,-100/$H$134,$H$134/100))/(1+IF($O$134&lt;0,-100/$O$134,$O$134/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="G135" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="13">
+        <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
+        <v/>
+      </c>
+      <c r="J135" s="16">
+        <f>IF($H$135="","",$F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))</f>
+        <v/>
+      </c>
+      <c r="K135" s="17">
+        <f>IF($H$135="","",MAX(0,($F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))/IF($H$135&lt;0,-100/$H$135,$H$135/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L135" s="18">
+        <f>IF($H$135="","",ROUND(MIN($K$135,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M135" s="12">
+        <f>IF($J$135="","",IF($J$135&lt;0,"Pass",IF($J$135&lt;'Settings'!$B$4,"Thin",IF($J$135&lt;0.06,"✅ Sharp band",IF($J$135&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N135" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.3% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O135" s="15" t="n"/>
+      <c r="P135" s="16">
+        <f>IF(OR($H$135="",$O$135=""),"",(1+IF($H$135&lt;0,-100/$H$135,$H$135/100))/(1+IF($O$135&lt;0,-100/$O$135,$O$135/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>0.5272</v>
+      </c>
+      <c r="G136" s="14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="13">
+        <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
+        <v/>
+      </c>
+      <c r="J136" s="16">
+        <f>IF($H$136="","",$F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))</f>
+        <v/>
+      </c>
+      <c r="K136" s="17">
+        <f>IF($H$136="","",MAX(0,($F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))/IF($H$136&lt;0,-100/$H$136,$H$136/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L136" s="18">
+        <f>IF($H$136="","",ROUND(MIN($K$136,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M136" s="12">
+        <f>IF($J$136="","",IF($J$136&lt;0,"Pass",IF($J$136&lt;'Settings'!$B$4,"Thin",IF($J$136&lt;0.06,"✅ Sharp band",IF($J$136&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N136" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.7% (fair -112). Your call.</t>
+        </is>
+      </c>
+      <c r="O136" s="15" t="n"/>
+      <c r="P136" s="16">
+        <f>IF(OR($H$136="",$O$136=""),"",(1+IF($H$136&lt;0,-100/$H$136,$H$136/100))/(1+IF($O$136&lt;0,-100/$O$136,$O$136/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Over 9</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="G137" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I137" s="13">
+        <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
+        <v/>
+      </c>
+      <c r="J137" s="16">
+        <f>IF($H$137="","",$F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))</f>
+        <v/>
+      </c>
+      <c r="K137" s="17">
+        <f>IF($H$137="","",MAX(0,($F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))/IF($H$137&lt;0,-100/$H$137,$H$137/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L137" s="18">
+        <f>IF($H$137="","",ROUND(MIN($K$137,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M137" s="12">
+        <f>IF($J$137="","",IF($J$137&lt;0,"Pass",IF($J$137&lt;'Settings'!$B$4,"Thin",IF($J$137&lt;0.06,"✅ Sharp band",IF($J$137&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N137" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.7% (fair +129). Your call.</t>
+        </is>
+      </c>
+      <c r="O137" s="15" t="n"/>
+      <c r="P137" s="16">
+        <f>IF(OR($H$137="",$O$137=""),"",(1+IF($H$137&lt;0,-100/$H$137,$H$137/100))/(1+IF($O$137&lt;0,-100/$O$137,$O$137/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D138" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Under 9</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I138" s="13">
+        <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
+        <v/>
+      </c>
+      <c r="J138" s="16">
+        <f>IF($H$138="","",$F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))</f>
+        <v/>
+      </c>
+      <c r="K138" s="17">
+        <f>IF($H$138="","",MAX(0,($F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))/IF($H$138&lt;0,-100/$H$138,$H$138/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L138" s="18">
+        <f>IF($H$138="","",ROUND(MIN($K$138,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M138" s="12">
+        <f>IF($J$138="","",IF($J$138&lt;0,"Pass",IF($J$138&lt;'Settings'!$B$4,"Thin",IF($J$138&lt;0.06,"✅ Sharp band",IF($J$138&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N138" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.6% (fair +110). Your call.</t>
+        </is>
+      </c>
+      <c r="O138" s="15" t="n"/>
+      <c r="P138" s="16">
+        <f>IF(OR($H$138="",$O$138=""),"",(1+IF($H$138&lt;0,-100/$H$138,$H$138/100))/(1+IF($O$138&lt;0,-100/$O$138,$O$138/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants -1.5</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="G139" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="I139" s="13">
+        <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
+        <v/>
+      </c>
+      <c r="J139" s="16">
+        <f>IF($H$139="","",$F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))</f>
+        <v/>
+      </c>
+      <c r="K139" s="17">
+        <f>IF($H$139="","",MAX(0,($F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))/IF($H$139&lt;0,-100/$H$139,$H$139/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L139" s="18">
+        <f>IF($H$139="","",ROUND(MIN($K$139,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M139" s="12">
+        <f>IF($J$139="","",IF($J$139&lt;0,"Pass",IF($J$139&lt;'Settings'!$B$4,"Thin",IF($J$139&lt;0.06,"✅ Sharp band",IF($J$139&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N139" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.7% (fair +140). Your call.</t>
+        </is>
+      </c>
+      <c r="O139" s="15" t="n"/>
+      <c r="P139" s="16">
+        <f>IF(OR($H$139="",$O$139=""),"",(1+IF($H$139&lt;0,-100/$H$139,$H$139/100))/(1+IF($O$139&lt;0,-100/$O$139,$O$139/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="D140" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies +1.5</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G140" s="14" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-145</v>
+      </c>
+      <c r="I140" s="13">
+        <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
+        <v/>
+      </c>
+      <c r="J140" s="16">
+        <f>IF($H$140="","",$F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))</f>
+        <v/>
+      </c>
+      <c r="K140" s="17">
+        <f>IF($H$140="","",MAX(0,($F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))/IF($H$140&lt;0,-100/$H$140,$H$140/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L140" s="18">
+        <f>IF($H$140="","",ROUND(MIN($K$140,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M140" s="12">
+        <f>IF($J$140="","",IF($J$140&lt;0,"Pass",IF($J$140&lt;'Settings'!$B$4,"Thin",IF($J$140&lt;0.06,"✅ Sharp band",IF($J$140&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N140" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.3% (fair -140). Your call.</t>
+        </is>
+      </c>
+      <c r="O140" s="15" t="n"/>
+      <c r="P140" s="16">
+        <f>IF(OR($H$140="",$O$140=""),"",(1+IF($H$140&lt;0,-100/$H$140,$H$140/100))/(1+IF($O$140&lt;0,-100/$O$140,$O$140/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="G141" s="14" t="n">
+        <v>158</v>
+      </c>
+      <c r="H141" s="15" t="n"/>
+      <c r="I141" s="13">
+        <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
+        <v/>
+      </c>
+      <c r="J141" s="16">
+        <f>IF($H$141="","",$F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))</f>
+        <v/>
+      </c>
+      <c r="K141" s="17">
+        <f>IF($H$141="","",MAX(0,($F$141*IF($H$141&lt;0,-100/$H$141,$H$141/100)-(1-$F$141))/IF($H$141&lt;0,-100/$H$141,$H$141/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L141" s="18">
+        <f>IF($H$141="","",ROUND(MIN($K$141,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M141" s="12">
+        <f>IF($J$141="","",IF($J$141&lt;0,"Pass",IF($J$141&lt;'Settings'!$B$4,"Thin",IF($J$141&lt;0.06,"✅ Sharp band",IF($J$141&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N141" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.7% (fair +158). Your call.</t>
+        </is>
+      </c>
+      <c r="O141" s="15" t="n"/>
+      <c r="P141" s="16">
+        <f>IF(OR($H$141="",$O$141=""),"",(1+IF($H$141&lt;0,-100/$H$141,$H$141/100))/(1+IF($O$141&lt;0,-100/$O$141,$O$141/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="n">
+        <v>0.6128</v>
+      </c>
+      <c r="G142" s="14" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H142" s="15" t="n"/>
+      <c r="I142" s="13">
+        <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
+        <v/>
+      </c>
+      <c r="J142" s="16">
+        <f>IF($H$142="","",$F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))</f>
+        <v/>
+      </c>
+      <c r="K142" s="17">
+        <f>IF($H$142="","",MAX(0,($F$142*IF($H$142&lt;0,-100/$H$142,$H$142/100)-(1-$F$142))/IF($H$142&lt;0,-100/$H$142,$H$142/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L142" s="18">
+        <f>IF($H$142="","",ROUND(MIN($K$142,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M142" s="12">
+        <f>IF($J$142="","",IF($J$142&lt;0,"Pass",IF($J$142&lt;'Settings'!$B$4,"Thin",IF($J$142&lt;0.06,"✅ Sharp band",IF($J$142&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N142" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.3% (fair -158). Your call.</t>
+        </is>
+      </c>
+      <c r="O142" s="15" t="n"/>
+      <c r="P142" s="16">
+        <f>IF(OR($H$142="",$O$142=""),"",(1+IF($H$142&lt;0,-100/$H$142,$H$142/100))/(1+IF($O$142&lt;0,-100/$O$142,$O$142/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="G143" s="14" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H143" s="15" t="n"/>
+      <c r="I143" s="13">
+        <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
+        <v/>
+      </c>
+      <c r="J143" s="16">
+        <f>IF($H$143="","",$F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))</f>
+        <v/>
+      </c>
+      <c r="K143" s="17">
+        <f>IF($H$143="","",MAX(0,($F$143*IF($H$143&lt;0,-100/$H$143,$H$143/100)-(1-$F$143))/IF($H$143&lt;0,-100/$H$143,$H$143/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L143" s="18">
+        <f>IF($H$143="","",ROUND(MIN($K$143,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M143" s="12">
+        <f>IF($J$143="","",IF($J$143&lt;0,"Pass",IF($J$143&lt;'Settings'!$B$4,"Thin",IF($J$143&lt;0.06,"✅ Sharp band",IF($J$143&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N143" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.3% (fair -114). Your call.</t>
+        </is>
+      </c>
+      <c r="O143" s="15" t="n"/>
+      <c r="P143" s="16">
+        <f>IF(OR($H$143="",$O$143=""),"",(1+IF($H$143&lt;0,-100/$H$143,$H$143/100))/(1+IF($O$143&lt;0,-100/$O$143,$O$143/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="G144" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="13">
+        <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
+        <v/>
+      </c>
+      <c r="J144" s="16">
+        <f>IF($H$144="","",$F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))</f>
+        <v/>
+      </c>
+      <c r="K144" s="17">
+        <f>IF($H$144="","",MAX(0,($F$144*IF($H$144&lt;0,-100/$H$144,$H$144/100)-(1-$F$144))/IF($H$144&lt;0,-100/$H$144,$H$144/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L144" s="18">
+        <f>IF($H$144="","",ROUND(MIN($K$144,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M144" s="12">
+        <f>IF($J$144="","",IF($J$144&lt;0,"Pass",IF($J$144&lt;'Settings'!$B$4,"Thin",IF($J$144&lt;0.06,"✅ Sharp band",IF($J$144&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N144" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.7% (fair +114). Your call.</t>
+        </is>
+      </c>
+      <c r="O144" s="15" t="n"/>
+      <c r="P144" s="16">
+        <f>IF(OR($H$144="",$O$144=""),"",(1+IF($H$144&lt;0,-100/$H$144,$H$144/100))/(1+IF($O$144&lt;0,-100/$O$144,$O$144/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="G145" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H145" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I145" s="13">
+        <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
+        <v/>
+      </c>
+      <c r="J145" s="16">
+        <f>IF($H$145="","",$F$145*IF($H$145&lt;0,-100/$H$145,$H$145/100)-(1-$F$145))</f>
+        <v/>
+      </c>
+      <c r="K145" s="17">
+        <f>IF($H$145="","",MAX(0,($F$145*IF($H$145&lt;0,-100/$H$145,$H$145/100)-(1-$F$145))/IF($H$145&lt;0,-100/$H$145,$H$145/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L145" s="18">
+        <f>IF($H$145="","",ROUND(MIN($K$145,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M145" s="12">
+        <f>IF($J$145="","",IF($J$145&lt;0,"Pass",IF($J$145&lt;'Settings'!$B$4,"Thin",IF($J$145&lt;0.06,"✅ Sharp band",IF($J$145&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N145" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.9% (fair +123). Your call.</t>
+        </is>
+      </c>
+      <c r="O145" s="15" t="n"/>
+      <c r="P145" s="16">
+        <f>IF(OR($H$145="",$O$145=""),"",(1+IF($H$145&lt;0,-100/$H$145,$H$145/100))/(1+IF($O$145&lt;0,-100/$O$145,$O$145/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>Under 8</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="G146" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I146" s="13">
+        <f>IF($H$146="","",IF($H$146&lt;0,-$H$146/(-$H$146+100),100/($H$146+100)))</f>
+        <v/>
+      </c>
+      <c r="J146" s="16">
+        <f>IF($H$146="","",$F$146*IF($H$146&lt;0,-100/$H$146,$H$146/100)-(1-$F$146))</f>
+        <v/>
+      </c>
+      <c r="K146" s="17">
+        <f>IF($H$146="","",MAX(0,($F$146*IF($H$146&lt;0,-100/$H$146,$H$146/100)-(1-$F$146))/IF($H$146&lt;0,-100/$H$146,$H$146/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L146" s="18">
+        <f>IF($H$146="","",ROUND(MIN($K$146,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M146" s="12">
+        <f>IF($J$146="","",IF($J$146&lt;0,"Pass",IF($J$146&lt;'Settings'!$B$4,"Thin",IF($J$146&lt;0.06,"✅ Sharp band",IF($J$146&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N146" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.9% (fair +118). Your call.</t>
+        </is>
+      </c>
+      <c r="O146" s="15" t="n"/>
+      <c r="P146" s="16">
+        <f>IF(OR($H$146="",$O$146=""),"",(1+IF($H$146&lt;0,-100/$H$146,$H$146/100))/(1+IF($O$146&lt;0,-100/$O$146,$O$146/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres +1.5</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="n">
+        <v>0.5966</v>
+      </c>
+      <c r="G147" s="14" t="n">
+        <v>-148</v>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-165</v>
+      </c>
+      <c r="I147" s="13">
+        <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
+        <v/>
+      </c>
+      <c r="J147" s="16">
+        <f>IF($H$147="","",$F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))</f>
+        <v/>
+      </c>
+      <c r="K147" s="17">
+        <f>IF($H$147="","",MAX(0,($F$147*IF($H$147&lt;0,-100/$H$147,$H$147/100)-(1-$F$147))/IF($H$147&lt;0,-100/$H$147,$H$147/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L147" s="18">
+        <f>IF($H$147="","",ROUND(MIN($K$147,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M147" s="12">
+        <f>IF($J$147="","",IF($J$147&lt;0,"Pass",IF($J$147&lt;'Settings'!$B$4,"Thin",IF($J$147&lt;0.06,"✅ Sharp band",IF($J$147&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N147" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.7% (fair -148). Your call.</t>
+        </is>
+      </c>
+      <c r="O147" s="15" t="n"/>
+      <c r="P147" s="16">
+        <f>IF(OR($H$147="",$O$147=""),"",(1+IF($H$147&lt;0,-100/$H$147,$H$147/100))/(1+IF($O$147&lt;0,-100/$O$147,$O$147/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays -1.5</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="G148" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="I148" s="13">
+        <f>IF($H$148="","",IF($H$148&lt;0,-$H$148/(-$H$148+100),100/($H$148+100)))</f>
+        <v/>
+      </c>
+      <c r="J148" s="16">
+        <f>IF($H$148="","",$F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))</f>
+        <v/>
+      </c>
+      <c r="K148" s="17">
+        <f>IF($H$148="","",MAX(0,($F$148*IF($H$148&lt;0,-100/$H$148,$H$148/100)-(1-$F$148))/IF($H$148&lt;0,-100/$H$148,$H$148/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L148" s="18">
+        <f>IF($H$148="","",ROUND(MIN($K$148,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M148" s="12">
+        <f>IF($J$148="","",IF($J$148&lt;0,"Pass",IF($J$148&lt;'Settings'!$B$4,"Thin",IF($J$148&lt;0.06,"✅ Sharp band",IF($J$148&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N148" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.3% (fair +148). Your call.</t>
+        </is>
+      </c>
+      <c r="O148" s="15" t="n"/>
+      <c r="P148" s="16">
+        <f>IF(OR($H$148="",$O$148=""),"",(1+IF($H$148&lt;0,-100/$H$148,$H$148/100))/(1+IF($O$148&lt;0,-100/$O$148,$O$148/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J106">
+  <conditionalFormatting sqref="J5:J148">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -17478,7 +20250,7 @@
         <v>204</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -17604,13 +20376,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4951</v>
+        <v>0.4927</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -17634,7 +20406,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -17670,10 +20442,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5049</v>
+        <v>0.5073</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>108</v>
@@ -17700,7 +20472,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -17732,17 +20504,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -7.5</t>
+          <t>Minnesota Lynx -5.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4536141029303052</v>
+        <v>0.5163300815727817</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>120</v>
+        <v>-107</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -17766,7 +20538,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -17798,17 +20570,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty +7.5</t>
+          <t>New York Liberty +5.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5463858970696948</v>
+        <v>0.4836699184272183</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-120</v>
+        <v>107</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17832,7 +20604,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -17874,7 +20646,7 @@
         <v>341</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -18000,13 +20772,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5870644226482148</v>
+        <v>0.5362</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-142</v>
+        <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -18030,7 +20802,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -18066,13 +20838,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4129355773517852</v>
+        <v>0.4638</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>111</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -18096,7 +20868,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -18132,10 +20904,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4344</v>
+        <v>0.4314</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>100</v>
@@ -18162,7 +20934,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -18198,13 +20970,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5656</v>
+        <v>0.5686</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -18228,7 +21000,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -18392,17 +21164,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 171</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5556700048059063</v>
+        <v>0.5275</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-125</v>
+        <v>-112</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -18426,7 +21198,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -18458,17 +21230,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 171</t>
+          <t>Under 170.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4211299951940937</v>
+        <v>0.4725</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -18492,7 +21264,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -18524,11 +21296,11 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -10</t>
+          <t>Las Vegas Aces -10.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4626</v>
+        <v>0.4625</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>116</v>
@@ -18558,7 +21330,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -18590,14 +21362,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +10</t>
+          <t>Phoenix Mercury +10.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5063</v>
+        <v>0.5375</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>-116</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>100</v>
@@ -18624,7 +21396,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -18660,14 +21432,12 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6195999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-163</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-138</v>
-      </c>
+        <v>-161</v>
+      </c>
+      <c r="H23" s="15" t="n"/>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
         <v/>
@@ -18690,7 +21460,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -18726,14 +21496,12 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3804</v>
+        <v>0.3825</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>163</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="H24" s="15" t="n"/>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
         <v/>
@@ -18756,7 +21524,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.2% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -18792,14 +21560,12 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3875999999999999</v>
+        <v>0.3563</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>158</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>156</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
         <v/>
@@ -18822,7 +21588,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -18858,14 +21624,12 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6437</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-158</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>-186</v>
-      </c>
+        <v>-181</v>
+      </c>
+      <c r="H26" s="15" t="n"/>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
         <v/>
@@ -18888,7 +21652,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -18924,14 +21688,12 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.2307</v>
+        <v>0.2121</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>333</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>317</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="H27" s="15" t="n"/>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
         <v/>
@@ -18954,7 +21716,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 23.1% (fair +333). Your call.</t>
+          <t>Model 21.2% (fair +371). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -18990,14 +21752,12 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.7693</v>
+        <v>0.7879</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-333</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>-300</v>
-      </c>
+        <v>-371</v>
+      </c>
+      <c r="H28" s="15" t="n"/>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
         <v/>
@@ -19020,7 +21780,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 76.9% (fair -333). Your call.</t>
+          <t>Model 78.8% (fair -371). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -19056,14 +21816,12 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3901</v>
+        <v>0.3925</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>156</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>163</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="H29" s="15" t="n"/>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
         <v/>
@@ -19086,7 +21844,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -19122,14 +21880,12 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6099</v>
+        <v>0.6075</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-156</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>-163</v>
-      </c>
+        <v>-155</v>
+      </c>
+      <c r="H30" s="15" t="n"/>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
         <v/>
@@ -19152,7 +21908,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>

--- a/data/output/workbook/2026-07-11.xlsx
+++ b/data/output/workbook/2026-07-11.xlsx
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10267950"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 17:01</t>
+          <t>2026-07-11 18:03</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6779,903 +6779,903 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>3.918</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>4.274</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.918</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.7</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>4.274</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.585</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>4.106</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.69</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.1</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>9.388</v>
+        <v>4.106</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.585</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>13th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.366</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8828,17 +8828,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6698999999999999</v>
+        <v>0.6388</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-203</v>
+        <v>-177</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 67.0% (fair -203). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8914,17 +8914,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6496</v>
+        <v>0.6698999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-185</v>
+        <v>-203</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -185). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8960,17 +8960,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8980,14 +8980,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6427</v>
+        <v>0.6496</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-180</v>
+        <v>-185</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 65.0% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6351</v>
+        <v>0.6437999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-174</v>
+        <v>-181</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9224,7 +9224,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9234,27 +9234,27 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.4466</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-117</v>
+        <v>124</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9310,17 +9310,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5554</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-148</v>
+        <v>-125</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9361,32 +9361,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.5434</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>124</v>
+        <v>-119</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5554</v>
+        <v>0.5605</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.0% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9512,13 +9512,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5424</v>
+        <v>0.5354</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-119</v>
+        <v>-115</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9574,11 +9574,11 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5339</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-115</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5555</v>
+        <v>0.5463</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-125</v>
+        <v>-120</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>109</v>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9706,17 +9706,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.518</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-115</v>
+        <v>-107</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5172</v>
+        <v>0.5402</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-107</v>
+        <v>-117</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9823,12 +9823,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Portland Fire @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9838,17 +9838,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 169.5</t>
+          <t>Over 174.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.539</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>-117</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9884,37 +9884,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 174.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.3991</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-117</v>
+        <v>151</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9950,37 +9950,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.648</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-121</v>
+        <v>-184</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>-147</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10016,17 +10016,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10036,17 +10036,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5681</v>
+        <v>0.4784</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-132</v>
+        <v>109</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>127</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.5402</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>151</v>
+        <v>-117</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10153,32 +10153,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.4859</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-111</v>
+        <v>106</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10214,17 +10214,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.648</v>
+        <v>0.5716</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-184</v>
+        <v>-133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-147</v>
+        <v>-113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 57.2% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10280,37 +10280,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4607</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10351,32 +10351,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.5158</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>106</v>
+        <v>-107</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10412,37 +10412,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.482</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11567,7 +11567,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4828</v>
+        <v>0.482</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>107</v>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5172</v>
+        <v>0.518</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>-107</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4625</v>
+        <v>0.4633</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>116</v>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5375</v>
+        <v>0.5367</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-116</v>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4518915</v>
+        <v>0.453894</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5481085</v>
+        <v>0.546106</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>133</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5555</v>
+        <v>0.5463</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-125</v>
+        <v>-120</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>109</v>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12029,10 +12029,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3538</v>
+        <v>0.3626</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>108</v>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3649</v>
+        <v>0.3562</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>165</v>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12161,10 +12161,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6351</v>
+        <v>0.6437999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-174</v>
+        <v>-181</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>170</v>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4576</v>
+        <v>0.4566</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>119</v>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +119). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5424</v>
+        <v>0.5434</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-119</v>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12887,10 +12887,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.502</v>
+        <v>0.5011</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>111</v>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.498</v>
+        <v>0.4989</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-112</v>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13943,10 +13943,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-148</v>
+        <v>-128</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>109</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 56.0% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.3141999999999999</v>
+        <v>0.3489</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>104</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 31.4% (fair +218). Your call.</t>
+          <t>Model 34.9% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.439</v>
+        <v>0.4368</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>144</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5609999999999999</v>
+        <v>0.5631999999999999</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-150</v>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5216000000000001</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-109</v>
@@ -14273,7 +14273,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4784</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>109</v>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4855</v>
+        <v>0.4593</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4221</v>
+        <v>0.4485</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>113</v>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14471,10 +14471,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5935</v>
+        <v>0.5944</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>-135</v>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.4% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14537,10 +14537,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4065</v>
+        <v>0.4056</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>133</v>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4434</v>
+        <v>0.4452</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14667,10 +14667,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5566</v>
+        <v>0.5548</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4858</v>
+        <v>0.4857</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>106</v>
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5142</v>
+        <v>0.5143</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>-106</v>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3785</v>
+        <v>0.3603</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6397</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-164</v>
+        <v>-178</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -164). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5177</v>
+        <v>0.5233</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-107</v>
+        <v>-110</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15437,10 +15437,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4823</v>
+        <v>0.4767</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>122</v>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 7</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
@@ -15509,7 +15509,7 @@
         <v>-117</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15565,17 +15565,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 7</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4615</v>
+        <v>0.3647</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -16295,13 +16295,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5681</v>
+        <v>0.5716</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 57.2% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4319</v>
+        <v>0.4284</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>117</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 42.8% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16427,10 +16427,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5228</v>
+        <v>0.5196</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>104</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16493,13 +16493,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4772</v>
+        <v>0.4804</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -17087,13 +17087,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4647</v>
+        <v>0.4654</v>
       </c>
       <c r="G103" s="14" t="n">
         <v>115</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.443</v>
+        <v>0.4423</v>
       </c>
       <c r="G104" s="14" t="n">
         <v>126</v>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17351,7 +17351,7 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.4834000000000001</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>107</v>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-107</v>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5158</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-111</v>
+        <v>-107</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>108</v>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17549,10 +17549,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.4842</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>-104</v>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.6369</v>
+        <v>0.6389</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-175</v>
+        <v>-177</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>-186</v>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.3631</v>
+        <v>0.3611</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H112" s="15" t="n">
         <v>180</v>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17747,13 +17747,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4119</v>
+        <v>0.4155</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17813,10 +17813,10 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5881</v>
+        <v>0.5845</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-143</v>
+        <v>-141</v>
       </c>
       <c r="H114" s="15" t="n">
         <v>-127</v>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4332</v>
+        <v>0.4219000000000001</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>127</v>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17945,10 +17945,10 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5668</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-131</v>
+        <v>-137</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>-127</v>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18011,10 +18011,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4745</v>
+        <v>0.4526</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>101</v>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18077,10 +18077,10 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4385000000000001</v>
+        <v>0.4605</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>105</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18143,10 +18143,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3922</v>
+        <v>0.3958</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>165</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18209,10 +18209,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.6042000000000001</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-155</v>
+        <v>-153</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-165</v>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18275,7 +18275,7 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4544484</v>
+        <v>0.4539864</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>120</v>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5455516</v>
+        <v>0.5460136</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>-120</v>
@@ -18407,10 +18407,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.5402</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-121</v>
+        <v>-117</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>100</v>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18473,10 +18473,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.4598</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>104</v>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18539,10 +18539,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3573</v>
+        <v>0.3612</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>160</v>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +180). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6427</v>
+        <v>0.6388</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-180</v>
+        <v>-177</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18799,13 +18799,13 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4944</v>
+        <v>0.4912</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18865,10 +18865,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5056</v>
+        <v>0.5087999999999999</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>-108</v>
@@ -18895,7 +18895,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -19191,7 +19191,7 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4728</v>
+        <v>0.4711</v>
       </c>
       <c r="G135" s="14" t="n">
         <v>112</v>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19255,7 +19255,7 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5272</v>
+        <v>0.5289</v>
       </c>
       <c r="G136" s="14" t="n">
         <v>-112</v>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19319,10 +19319,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>100</v>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19385,10 +19385,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4824000000000001</v>
+        <v>0.4864000000000001</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>104</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19451,10 +19451,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.3967</v>
+        <v>0.3959</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>150</v>
@@ -19481,7 +19481,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.6041000000000001</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>-145</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19711,10 +19711,10 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.5241</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19775,10 +19775,10 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.4759</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19839,10 +19839,10 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.4881</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H145" s="15" t="n">
         <v>104</v>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19905,10 +19905,10 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.5119</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>100</v>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.5966</v>
+        <v>0.5974</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>-148</v>
@@ -20037,7 +20037,7 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.4034</v>
+        <v>0.4026</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>148</v>
@@ -20646,7 +20646,7 @@
         <v>312</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -20772,7 +20772,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.539</v>
+        <v>0.5402</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>-117</v>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20838,13 +20838,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.461</v>
+        <v>0.4598</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20910,7 +20910,7 @@
         <v>116</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -20976,7 +20976,7 @@
         <v>-116</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -21036,10 +21036,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6175</v>
+        <v>0.6054</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-161</v>
+        <v>-153</v>
       </c>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="13">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -161). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -21100,10 +21100,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3825</v>
+        <v>0.3946</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="13">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +161). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -21627,22 +21627,22 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2497</v>
+        <v>0.2495</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.409</v>
+        <v>0.4105</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-55.98</v>
+        <v>-54.56</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-10.96</v>
+        <v>-10.62</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>4.41</v>
@@ -21658,22 +21658,22 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2502</v>
+        <v>0.2499</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4062</v>
+        <v>0.4079</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-54.78</v>
+        <v>-53.36</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-12.09</v>
+        <v>-11.7</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>6.29</v>
@@ -21762,7 +21762,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=389, ECE 0.044 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=390, ECE 0.043 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21895,16 +21895,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.6404</v>
+        <v>0.6402</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.5682</v>
+        <v>0.5778</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.0722</v>
+        <v>-0.0625</v>
       </c>
     </row>
     <row r="23">

--- a/data/output/workbook/2026-07-11.xlsx
+++ b/data/output/workbook/2026-07-11.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10534650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 18:03</t>
+          <t>2026-07-11 19:01</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4915,171 +4915,250 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs New York Mets defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.862</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.275</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.2</v>
+        <v>8.304</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.862</v>
+        <v>7.918</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.304</v>
+        <v>0.739</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -5143,22 +5222,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.918</v>
+        <v>0.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.739</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5222,313 +5301,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.918</v>
+        <v>9.061</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.239000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.392</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.8</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.061</v>
+        <v>0.542</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Boston Red Sox defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.069</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.069</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
+        <v>7.306</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.467</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.013</v>
+        <v>8.391</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.306</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -5592,22 +5671,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.391</v>
+        <v>1.217</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5671,151 +5750,72 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.217</v>
+        <v>8.587</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.542</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.367</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.587</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6762,7 +6762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6779,246 +6779,167 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>3.918</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.274</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.918</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>3.7</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.694</v>
+        <v>4.274</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.959</v>
+        <v>7.735</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7082,22 +7003,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.082</v>
+        <v>7.694</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8</v>
+        <v>0.959</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -7161,317 +7082,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>1.082</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H74" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.585</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.106</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.69</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>4.1</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.939</v>
+        <v>4.106</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.918</v>
+        <v>8.286</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7535,22 +7456,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.143</v>
+        <v>7.939</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.816</v>
+        <v>0.918</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -7614,68 +7535,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>9.388</v>
+        <v>1.143</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.585</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
         <is>
           <t>13th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.366</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8828,17 +8828,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6388</v>
+        <v>0.6698999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-177</v>
+        <v>-203</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8914,17 +8914,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6698999999999999</v>
+        <v>0.6496</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-203</v>
+        <v>-185</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 67.0% (fair -203). Your call.</t>
+          <t>Model 65.0% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8980,17 +8980,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6496</v>
+        <v>0.6437999999999999</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-185</v>
+        <v>-181</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -185). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9026,7 +9026,7 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-181</v>
+        <v>-177</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 63.8% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9229,32 +9229,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>124</v>
+        <v>-148</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9295,32 +9295,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5554</v>
+        <v>0.4466</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-125</v>
+        <v>124</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9376,14 +9376,14 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5554</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-119</v>
+        <v>-125</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>122</v>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5434</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-128</v>
+        <v>-119</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -128). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.518</v>
+        <v>0.5111</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-107</v>
+        <v>-105</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>120</v>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9818,37 +9818,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 174.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-117</v>
+        <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9889,32 +9889,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.5256</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>151</v>
+        <v>-111</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9950,37 +9950,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.648</v>
+        <v>0.5466</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-184</v>
+        <v>-121</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-147</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10021,12 +10021,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10036,17 +10036,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.648</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>109</v>
+        <v>-184</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>127</v>
+        <v>-147</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10082,12 +10082,12 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10102,17 +10102,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5402</v>
+        <v>0.4889</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-117</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10148,17 +10148,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10168,17 +10168,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.4779</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5716</v>
+        <v>0.4859</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-133</v>
+        <v>106</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10361,22 +10361,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5158</v>
+        <v>0.5686</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-107</v>
+        <v>-132</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10417,32 +10417,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.482</v>
+        <v>0.439</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.482</v>
+        <v>0.4889</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>122</v>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.518</v>
+        <v>0.5111</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-107</v>
+        <v>-105</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>120</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4633</v>
+        <v>0.4681</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>122</v>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11765,10 +11765,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5367</v>
+        <v>0.5319</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-116</v>
+        <v>-114</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-122</v>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4242</v>
+        <v>0.4233</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>136</v>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5758</v>
+        <v>0.5767</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-136</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.542</v>
+        <v>0.541</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>-118</v>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>118</v>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3961</v>
+        <v>0.3954</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>150</v>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +152). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6039</v>
+        <v>0.6046</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-156</v>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -152). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -13943,10 +13943,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-128</v>
+        <v>-148</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>109</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -128). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.3489</v>
+        <v>0.3141999999999999</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>104</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +187). Your call.</t>
+          <t>Model 31.4% (fair +218). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4368</v>
+        <v>0.439</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>144</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5631999999999999</v>
+        <v>0.5609999999999999</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-150</v>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5216000000000001</v>
+        <v>0.5221</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-109</v>
@@ -14273,7 +14273,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4779</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>109</v>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4593</v>
+        <v>0.4855</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4485</v>
+        <v>0.4221</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>113</v>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14471,10 +14471,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5944</v>
+        <v>0.5935</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-147</v>
+        <v>-146</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>-135</v>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -147). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14537,10 +14537,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4056</v>
+        <v>0.4065</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>133</v>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +147). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4452</v>
+        <v>0.4463</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14667,10 +14667,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5548</v>
+        <v>0.5537</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3603</v>
+        <v>0.3575</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 36.0% (fair +178). Your call.</t>
+          <t>Model 35.8% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6397</v>
+        <v>0.6425</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-178</v>
+        <v>-180</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 64.0% (fair -178). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5233</v>
+        <v>0.5206999999999999</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15437,10 +15437,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4767</v>
+        <v>0.4793</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>122</v>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15503,10 +15503,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.5189</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>-104</v>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15569,10 +15569,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.3647</v>
+        <v>0.3832</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>125</v>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15635,10 +15635,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5919</v>
+        <v>0.5931</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>-150</v>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4081</v>
+        <v>0.4069</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>138</v>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15899,13 +15899,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.4765</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15965,13 +15965,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5141</v>
+        <v>0.5235000000000001</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16031,10 +16031,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4012</v>
+        <v>0.4063</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>144</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5988</v>
+        <v>0.5937</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-149</v>
+        <v>-146</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-156</v>
+        <v>-144</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16295,10 +16295,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5716</v>
+        <v>0.5686</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>-113</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,13 +16361,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4284</v>
+        <v>0.4314</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4453</v>
+        <v>0.4489</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17021,10 +17021,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5547</v>
+        <v>0.5511</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-125</v>
+        <v>-123</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-127</v>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17219,13 +17219,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3563</v>
+        <v>0.352</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.2% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17285,10 +17285,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-181</v>
+        <v>-184</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>-185</v>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17351,7 +17351,7 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.4837</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>107</v>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5163</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-107</v>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5158</v>
+        <v>0.5256</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-107</v>
+        <v>-111</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>108</v>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17549,10 +17549,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4842</v>
+        <v>0.4744</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>-104</v>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.6389</v>
+        <v>0.638</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-177</v>
+        <v>-176</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>-186</v>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17681,13 +17681,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.3611</v>
+        <v>0.362</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17747,10 +17747,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4155</v>
+        <v>0.4184</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>122</v>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17813,13 +17813,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5845</v>
+        <v>0.5816</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-141</v>
+        <v>-139</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4219000000000001</v>
+        <v>0.4119</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>127</v>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17945,10 +17945,10 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5881</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-137</v>
+        <v>-143</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>-127</v>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18011,10 +18011,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4526</v>
+        <v>0.4691</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>101</v>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18077,10 +18077,10 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4605</v>
+        <v>0.4437999999999999</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>105</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18143,10 +18143,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3958</v>
+        <v>0.3976</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>165</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 39.8% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18209,10 +18209,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6042000000000001</v>
+        <v>0.6024</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-153</v>
+        <v>-152</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-165</v>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 60.2% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18275,7 +18275,7 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4539864</v>
+        <v>0.4539732</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>120</v>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5460136</v>
+        <v>0.5460268</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>-120</v>
@@ -18407,10 +18407,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5402</v>
+        <v>0.5466</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-117</v>
+        <v>-121</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>100</v>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18473,10 +18473,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4598</v>
+        <v>0.4534</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>104</v>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18539,13 +18539,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3612</v>
+        <v>0.3616</v>
       </c>
       <c r="G125" s="14" t="n">
         <v>177</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.2% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6388</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="G126" s="14" t="n">
         <v>-177</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.8% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18671,10 +18671,10 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.3918</v>
+        <v>0.3911</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H127" s="15" t="n"/>
       <c r="I127" s="13">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18735,10 +18735,10 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6082</v>
+        <v>0.6089</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="H128" s="15" t="n"/>
       <c r="I128" s="13">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18799,10 +18799,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4912</v>
+        <v>0.5023</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>104</v>
+        <v>-101</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>104</v>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18865,10 +18865,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5087999999999999</v>
+        <v>0.4977</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-104</v>
+        <v>101</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>-108</v>
@@ -18895,7 +18895,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18931,10 +18931,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.4</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>174</v>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18997,10 +18997,10 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.6009</v>
+        <v>0.6</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-151</v>
+        <v>-150</v>
       </c>
       <c r="H132" s="15" t="n">
         <v>-170</v>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19191,10 +19191,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4711</v>
+        <v>0.4611</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H135" s="15" t="n"/>
       <c r="I135" s="13">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19255,10 +19255,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5389</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-112</v>
+        <v>-117</v>
       </c>
       <c r="H136" s="15" t="n"/>
       <c r="I136" s="13">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19319,10 +19319,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.511</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>100</v>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19385,10 +19385,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4864000000000001</v>
+        <v>0.489</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>104</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19451,10 +19451,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.3959</v>
+        <v>0.3995</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>150</v>
@@ -19481,7 +19481,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.6041000000000001</v>
+        <v>0.6005</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-153</v>
+        <v>-150</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>-145</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19711,10 +19711,10 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.5327</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>-110</v>
+        <v>-114</v>
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19775,10 +19775,10 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.4673</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19839,10 +19839,10 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4881</v>
+        <v>0.4819</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H145" s="15" t="n">
         <v>104</v>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19905,10 +19905,10 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5119</v>
+        <v>0.5181</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>100</v>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.5974</v>
+        <v>0.5966</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>-148</v>
@@ -20037,7 +20037,7 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.4026</v>
+        <v>0.4034</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>148</v>
@@ -20100,7 +20100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20225,12 +20225,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -20240,17 +20240,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2266114000000001</v>
+        <v>0.24286</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>614</v>
+        <v>320</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 22.7% (fair +341). Your call.</t>
+          <t>Model 24.3% (fair +312). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20291,12 +20291,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -20306,17 +20306,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7733885999999999</v>
+        <v>0.75714</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-341</v>
+        <v>-312</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 77.3% (fair -341). Your call.</t>
+          <t>Model 75.7% (fair -312). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -20357,12 +20357,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -20372,17 +20372,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 174.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5402</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-117</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -20438,17 +20438,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 174.5</t>
+          <t>Under 169.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4602000000000001</v>
+        <v>0.4598</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -20504,17 +20504,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -13.5</t>
+          <t>Las Vegas Aces -9.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3926414967183107</v>
+        <v>0.4636117807798515</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -20555,12 +20555,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20570,17 +20570,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Phoenix Mercury +9.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6073585032816893</v>
+        <v>0.5363882192201485</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-155</v>
+        <v>-116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-102</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -20616,17 +20616,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -20636,18 +20636,16 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.24286</v>
+        <v>0.6054</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>312</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>310</v>
-      </c>
+        <v>-153</v>
+      </c>
+      <c r="H11" s="15" t="n"/>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
         <v/>
@@ -20670,7 +20668,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 24.3% (fair +312). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -20682,17 +20680,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -20702,18 +20700,16 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.75714</v>
+        <v>0.3946</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-312</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>-115</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="H12" s="15" t="n"/>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
         <v/>
@@ -20736,7 +20732,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 75.7% (fair -312). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -20748,38 +20744,36 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 169.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5402</v>
+        <v>0.3563</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>108</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H13" s="15" t="n"/>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
         <v/>
@@ -20802,7 +20796,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20814,38 +20808,36 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 169.5</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4598</v>
+        <v>0.6437</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>100</v>
-      </c>
+        <v>-181</v>
+      </c>
+      <c r="H14" s="15" t="n"/>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
         <v/>
@@ -20868,7 +20860,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20880,38 +20872,36 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -9.5</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4636117807798515</v>
+        <v>0.2121</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="H15" s="15" t="n"/>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
         <v/>
@@ -20934,7 +20924,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 21.2% (fair +371). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -20946,38 +20936,36 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +9.5</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5363882192201485</v>
+        <v>0.7879</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-116</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>108</v>
-      </c>
+        <v>-371</v>
+      </c>
+      <c r="H16" s="15" t="n"/>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
         <v/>
@@ -21000,7 +20988,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 78.8% (fair -371). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -21017,12 +21005,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -21032,14 +21020,14 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6054</v>
+        <v>0.3925</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-153</v>
+        <v>155</v>
       </c>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="13">
@@ -21064,7 +21052,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -21081,12 +21069,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -21096,14 +21084,14 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3946</v>
+        <v>0.6075</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>153</v>
+        <v>-155</v>
       </c>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="13">
@@ -21128,7 +21116,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -21137,393 +21125,9 @@
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Seattle Storm @ Washington Mystics</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Seattle Storm</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>0.3563</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>181</v>
-      </c>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13">
-        <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
-        <v/>
-      </c>
-      <c r="J19" s="16">
-        <f>IF($H$19="","",$F$19*IF($H$19&lt;0,-100/$H$19,$H$19/100)-(1-$F$19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="17">
-        <f>IF($H$19="","",MAX(0,($F$19*IF($H$19&lt;0,-100/$H$19,$H$19/100)-(1-$F$19))/IF($H$19&lt;0,-100/$H$19,$H$19/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L19" s="18">
-        <f>IF($H$19="","",ROUND(MIN($K$19,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M19" s="12">
-        <f>IF($J$19="","",IF($J$19&lt;0,"Pass",IF($J$19&lt;'Settings'!$B$4,"Thin",IF($J$19&lt;0.06,"✅ Sharp band",IF($J$19&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N19" s="19" t="inlineStr">
-        <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
-        </is>
-      </c>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="16">
-        <f>IF(OR($H$19="",$O$19=""),"",(1+IF($H$19&lt;0,-100/$H$19,$H$19/100))/(1+IF($O$19&lt;0,-100/$O$19,$O$19/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Seattle Storm @ Washington Mystics</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>0.6437</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>-181</v>
-      </c>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13">
-        <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
-        <v/>
-      </c>
-      <c r="J20" s="16">
-        <f>IF($H$20="","",$F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="17">
-        <f>IF($H$20="","",MAX(0,($F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))/IF($H$20&lt;0,-100/$H$20,$H$20/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L20" s="18">
-        <f>IF($H$20="","",ROUND(MIN($K$20,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M20" s="12">
-        <f>IF($J$20="","",IF($J$20&lt;0,"Pass",IF($J$20&lt;'Settings'!$B$4,"Thin",IF($J$20&lt;0.06,"✅ Sharp band",IF($J$20&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N20" s="19" t="inlineStr">
-        <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
-        </is>
-      </c>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="16">
-        <f>IF(OR($H$20="",$O$20=""),"",(1+IF($H$20&lt;0,-100/$H$20,$H$20/100))/(1+IF($O$20&lt;0,-100/$O$20,$O$20/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Chicago Sky @ Dallas Wings</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>0.2121</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>371</v>
-      </c>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="13">
-        <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
-        <v/>
-      </c>
-      <c r="J21" s="16">
-        <f>IF($H$21="","",$F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="17">
-        <f>IF($H$21="","",MAX(0,($F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))/IF($H$21&lt;0,-100/$H$21,$H$21/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L21" s="18">
-        <f>IF($H$21="","",ROUND(MIN($K$21,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M21" s="12">
-        <f>IF($J$21="","",IF($J$21&lt;0,"Pass",IF($J$21&lt;'Settings'!$B$4,"Thin",IF($J$21&lt;0.06,"✅ Sharp band",IF($J$21&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N21" s="19" t="inlineStr">
-        <is>
-          <t>Model 21.2% (fair +371). Your call.</t>
-        </is>
-      </c>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="16">
-        <f>IF(OR($H$21="",$O$21=""),"",(1+IF($H$21&lt;0,-100/$H$21,$H$21/100))/(1+IF($O$21&lt;0,-100/$O$21,$O$21/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Chicago Sky @ Dallas Wings</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>0.7879</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>-371</v>
-      </c>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="13">
-        <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
-        <v/>
-      </c>
-      <c r="J22" s="16">
-        <f>IF($H$22="","",$F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="17">
-        <f>IF($H$22="","",MAX(0,($F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))/IF($H$22&lt;0,-100/$H$22,$H$22/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L22" s="18">
-        <f>IF($H$22="","",ROUND(MIN($K$22,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M22" s="12">
-        <f>IF($J$22="","",IF($J$22&lt;0,"Pass",IF($J$22&lt;'Settings'!$B$4,"Thin",IF($J$22&lt;0.06,"✅ Sharp band",IF($J$22&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N22" s="19" t="inlineStr">
-        <is>
-          <t>Model 78.8% (fair -371). Your call.</t>
-        </is>
-      </c>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16">
-        <f>IF(OR($H$22="",$O$22=""),"",(1+IF($H$22&lt;0,-100/$H$22,$H$22/100))/(1+IF($O$22&lt;0,-100/$O$22,$O$22/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>Indiana Fever</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>0.3925</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>155</v>
-      </c>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="13">
-        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
-        <v/>
-      </c>
-      <c r="J23" s="16">
-        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="17">
-        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L23" s="18">
-        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M23" s="12">
-        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N23" s="19" t="inlineStr">
-        <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
-        </is>
-      </c>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="16">
-        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>0.6075</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13">
-        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
-        <v/>
-      </c>
-      <c r="J24" s="16">
-        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
-        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L24" s="18">
-        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M24" s="12">
-        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N24" s="19" t="inlineStr">
-        <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
-        </is>
-      </c>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="16">
-        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J24">
+  <conditionalFormatting sqref="J5:J18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -21627,10 +21231,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2495</v>
+        <v>0.2494</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>518</v>
@@ -21658,10 +21262,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2499</v>
+        <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>460</v>
@@ -21762,7 +21366,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=390, ECE 0.043 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=391, ECE 0.043 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21876,16 +21480,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.543</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0009</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-11.xlsx
+++ b/data/output/workbook/2026-07-11.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10534650"/>
+    <ext cx="10125075" cy="10687050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 19:01</t>
+          <t>2026-07-11 20:06</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4915,250 +4915,171 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.275</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.862</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.275</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.2</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.918</v>
+        <v>4.862</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.739</v>
+        <v>8.304</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -5222,22 +5143,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.239000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5301,313 +5222,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.392</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.542</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.069</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.013</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.069</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>3.467</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.391</v>
+        <v>4.013</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -5671,22 +5592,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.217</v>
+        <v>8.391</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5750,72 +5671,151 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.587</v>
+        <v>1.217</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.542</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J81" s="34" t="inlineStr">
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6762,7 +6762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6779,167 +6779,325 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.918</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.274</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.918</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>0.959</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.7</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.274</v>
+        <v>1.082</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.735</v>
+        <v>8</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7003,396 +7161,396 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.694</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.082</v>
+        <v>0.585</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.531000000000001</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+      <c r="K77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.106</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.1</v>
+        <v>0.918</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.106</v>
+        <v>1.143</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.286</v>
+        <v>7.816</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7456,226 +7614,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.939</v>
+        <v>9.388</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.585</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.433</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.143</v>
+        <v>0.366</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>9.388</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6698999999999999</v>
+        <v>0.6471</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-203</v>
+        <v>-183</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 67.0% (fair -203). Your call.</t>
+          <t>Model 64.7% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8914,17 +8914,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6496</v>
+        <v>0.6615</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-185</v>
+        <v>-195</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -185). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8960,7 +8960,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -8984,13 +8984,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-181</v>
+        <v>-177</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 63.8% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9046,14 +9046,14 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6384000000000001</v>
+        <v>0.6515</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-177</v>
+        <v>-187</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -177). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9112,17 +9112,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6129</v>
+        <v>0.6423</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-158</v>
+        <v>-180</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9178,17 +9178,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5534</v>
+        <v>0.6169</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-124</v>
+        <v>-161</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9224,7 +9224,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9234,27 +9234,27 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5868</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-148</v>
+        <v>-142</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9310,14 +9310,14 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.5493</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>124</v>
+        <v>-122</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>178</v>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9356,37 +9356,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5554</v>
+        <v>0.5647</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-125</v>
+        <v>-130</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9422,37 +9422,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5387</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9503,22 +9503,22 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.4507</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-115</v>
+        <v>122</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9554,7 +9554,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9574,17 +9574,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 7</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.6259</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-115</v>
+        <v>-167</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9620,17 +9620,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5463</v>
+        <v>0.6404000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-120</v>
+        <v>-178</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>109</v>
+        <v>-105</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9686,37 +9686,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5111</v>
+        <v>0.4613</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-105</v>
+        <v>117</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 169.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5402</v>
+        <v>0.5603</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9818,37 +9818,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4</v>
+        <v>0.556</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>150</v>
+        <v>-125</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9884,17 +9884,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5783</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-111</v>
+        <v>-137</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9950,17 +9950,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9970,17 +9970,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5466</v>
+        <v>0.5322</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-121</v>
+        <v>-114</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10016,37 +10016,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.648</v>
+        <v>0.4353</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-184</v>
+        <v>130</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-147</v>
+        <v>165</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4889</v>
+        <v>0.5292</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>105</v>
+        <v>-112</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10153,32 +10153,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.5487</v>
       </c>
       <c r="G25" s="14" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H25" s="15" t="n">
         <v>109</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>127</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10214,37 +10214,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.5119</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10280,37 +10280,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Phoenix Mercury @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.5402</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>117</v>
+        <v>-117</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10351,32 +10351,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Toronto Tempo +6.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5686</v>
+        <v>0.5429</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-132</v>
+        <v>-119</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10412,37 +10412,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.439</v>
+        <v>0.5256</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>128</v>
+        <v>-111</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10775,10 +10775,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4646</v>
+        <v>0.4678</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>117</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5322</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>117</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.4507</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5534</v>
+        <v>0.5493</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.5292</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>117</v>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4661</v>
+        <v>0.4708</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>117</v>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3504</v>
+        <v>0.3529</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>178</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +185). Your call.</t>
+          <t>Model 35.3% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11369,10 +11369,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6496</v>
+        <v>0.6471</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-185</v>
+        <v>-183</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -185). Your call.</t>
+          <t>Model 64.7% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11567,7 +11567,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4889</v>
+        <v>0.4881</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>105</v>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5111</v>
+        <v>0.5119</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>-105</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4681</v>
+        <v>0.4691</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>122</v>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11765,10 +11765,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5319</v>
+        <v>0.5308999999999999</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-122</v>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.453894</v>
+        <v>0.4534589999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.546106</v>
+        <v>0.5465410000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>133</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5463</v>
+        <v>0.5487</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>109</v>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12029,10 +12029,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3626</v>
+        <v>0.3601</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>108</v>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +176). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3562</v>
+        <v>0.3577</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>165</v>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.8% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12161,10 +12161,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-181</v>
+        <v>-180</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>170</v>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12359,10 +12359,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.541</v>
+        <v>0.5359</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>-113</v>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.459</v>
+        <v>0.4641</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>113</v>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3954</v>
+        <v>0.395</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>153</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6046</v>
+        <v>0.605</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-153</v>
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4566</v>
+        <v>0.444</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>122</v>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12821,10 +12821,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.556</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-119</v>
+        <v>-125</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>122</v>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12887,10 +12887,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5011</v>
+        <v>0.5019</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-100</v>
+        <v>-101</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>111</v>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4989</v>
+        <v>0.4981</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-112</v>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4281</v>
+        <v>0.4277</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>134</v>
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5719</v>
+        <v>0.5723</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>-134</v>
@@ -13151,10 +13151,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4796</v>
+        <v>0.4729</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>109</v>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13217,10 +13217,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.428</v>
+        <v>0.4348</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>108</v>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13283,10 +13283,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3871</v>
+        <v>0.3831</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>153</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13349,10 +13349,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6129</v>
+        <v>0.6169</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-158</v>
+        <v>-161</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>165</v>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13415,10 +13415,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.487</v>
+        <v>0.4842</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>100</v>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13481,10 +13481,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.513</v>
+        <v>0.5158</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>100</v>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5554</v>
+        <v>0.5603</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>122</v>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4446</v>
+        <v>0.4397</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>100</v>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13679,10 +13679,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3301</v>
+        <v>0.3385</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>180</v>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 33.0% (fair +203). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6698999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-203</v>
+        <v>-195</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>170</v>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 67.0% (fair -203). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13943,10 +13943,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5783</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-148</v>
+        <v>-137</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>109</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.3141999999999999</v>
+        <v>0.3323</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>104</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 31.4% (fair +218). Your call.</t>
+          <t>Model 33.2% (fair +201). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.439</v>
+        <v>0.4375</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>144</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 43.8% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5609999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-150</v>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.2% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5216000000000001</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-109</v>
@@ -14273,7 +14273,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4784</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>109</v>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4855</v>
+        <v>0.4801</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>105</v>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4221</v>
+        <v>0.4275</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>113</v>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14471,10 +14471,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5935</v>
+        <v>0.5945</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>-135</v>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14537,10 +14537,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4065</v>
+        <v>0.4055</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>133</v>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4463</v>
+        <v>0.4434</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14667,10 +14667,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5537</v>
+        <v>0.5566</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3575</v>
+        <v>0.3589</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +180). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6425</v>
+        <v>0.6411</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-180</v>
+        <v>-179</v>
       </c>
       <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -180). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5206999999999999</v>
+        <v>0.4196</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-109</v>
+        <v>138</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-117</v>
+        <v>-106</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15437,13 +15437,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4793</v>
+        <v>0.5804</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>109</v>
+        <v>-138</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15503,13 +15503,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5189</v>
+        <v>0.6259</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-108</v>
+        <v>-167</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15569,13 +15569,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.3832</v>
+        <v>0.2834</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 28.3% (fair +253). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5931</v>
+        <v>0.6409</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-146</v>
+        <v>-178</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15701,13 +15701,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4069</v>
+        <v>0.3591</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4258</v>
+        <v>0.4248</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>135</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15833,13 +15833,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5742</v>
+        <v>0.5752</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>-135</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-133</v>
+        <v>-135</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16031,10 +16031,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4063</v>
+        <v>0.4049</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>144</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5937</v>
+        <v>0.5951</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16163,13 +16163,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5141</v>
+        <v>0.4882</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-106</v>
+        <v>105</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-122</v>
+        <v>-108</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16229,13 +16229,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.5118</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16276,32 +16276,32 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5686</v>
+        <v>0.4526</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-132</v>
+        <v>121</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-113</v>
+        <v>-105</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16342,32 +16342,32 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4314</v>
+        <v>0.4603</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>113</v>
+        <v>-110</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16408,32 +16408,32 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5196</v>
+        <v>0.6309</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-108</v>
+        <v>-171</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>104</v>
+        <v>-170</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16474,32 +16474,32 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4804</v>
+        <v>0.3691</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-104</v>
+        <v>146</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16550,22 +16550,22 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5393</v>
+        <v>0.5751999999999999</v>
       </c>
       <c r="G95" s="14" t="n">
+        <v>-135</v>
+      </c>
+      <c r="H95" s="15" t="n">
         <v>-117</v>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-144</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16616,22 +16616,22 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.4248</v>
       </c>
       <c r="G96" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="H96" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>133</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -16682,22 +16682,22 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4569</v>
+        <v>0.5085</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>119</v>
+        <v>-103</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
@@ -16748,22 +16748,22 @@
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5431</v>
+        <v>0.4915</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-119</v>
+        <v>103</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -16814,22 +16814,22 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4918</v>
+        <v>0.5379</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>103</v>
+        <v>-116</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>100</v>
+        <v>-138</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
@@ -16880,22 +16880,22 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5082</v>
+        <v>0.4621</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-103</v>
+        <v>116</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -16951,17 +16951,17 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4489</v>
+        <v>0.4768</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
@@ -17017,17 +17017,17 @@
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5511</v>
+        <v>0.5232</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-123</v>
+        <v>-110</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-127</v>
+        <v>-104</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -17083,17 +17083,17 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4654</v>
+        <v>0.4897</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
@@ -17149,17 +17149,17 @@
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4423</v>
+        <v>0.5103</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>126</v>
+        <v>-104</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17210,22 +17210,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.352</v>
+        <v>0.4499</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 35.2% (fair +184). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17276,22 +17276,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.648</v>
+        <v>0.5501</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-184</v>
+        <v>-122</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-185</v>
+        <v>-125</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -17342,22 +17342,22 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.4654</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>100</v>
+        <v>-103</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
@@ -17408,22 +17408,22 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.4423</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-107</v>
+        <v>126</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -17474,22 +17474,22 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.3485</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-111</v>
+        <v>187</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
@@ -17540,22 +17540,22 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners +1.5</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.6515</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>111</v>
+        <v>-187</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17606,22 +17606,22 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.638</v>
+        <v>0.4805</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-176</v>
+        <v>108</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-186</v>
+        <v>104</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17672,22 +17672,22 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.362</v>
+        <v>0.5195</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>176</v>
+        <v>-108</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 36.2% (fair +176). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -17738,22 +17738,22 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4184</v>
+        <v>0.5256</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>139</v>
+        <v>-111</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
@@ -17804,22 +17804,22 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.4744</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-139</v>
+        <v>111</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-122</v>
+        <v>-104</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17860,32 +17860,32 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4119</v>
+        <v>0.6358</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>143</v>
+        <v>-175</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>127</v>
+        <v>-182</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17926,32 +17926,32 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5881</v>
+        <v>0.3642</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-143</v>
+        <v>175</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-127</v>
+        <v>180</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17992,32 +17992,32 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4691</v>
+        <v>0.4477</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18058,32 +18058,32 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4437999999999999</v>
+        <v>0.5523</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>125</v>
+        <v>-123</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>105</v>
+        <v>-115</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18124,32 +18124,32 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3976</v>
+        <v>0.5216</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>152</v>
+        <v>-109</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +152). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18190,32 +18190,32 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6024</v>
+        <v>0.4784</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-152</v>
+        <v>109</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-165</v>
+        <v>-105</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -152). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18256,32 +18256,32 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4539732</v>
+        <v>0.4132</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18322,32 +18322,32 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5460268</v>
+        <v>0.5868</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-120</v>
+        <v>-142</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -18398,22 +18398,22 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5466</v>
+        <v>0.4184</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-121</v>
+        <v>139</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
@@ -18464,22 +18464,22 @@
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4534</v>
+        <v>0.5816</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>121</v>
+        <v>-139</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>104</v>
+        <v>-122</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -18530,22 +18530,22 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3616</v>
+        <v>0.4843</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 36.2% (fair +177). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18586,7 +18586,7 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
@@ -18596,22 +18596,22 @@
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6384000000000001</v>
+        <v>0.4286</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-177</v>
+        <v>133</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -177). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18652,31 +18652,33 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.3911</v>
+        <v>0.4353</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>156</v>
-      </c>
-      <c r="H127" s="15" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>165</v>
+      </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
         <v/>
@@ -18699,7 +18701,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18716,31 +18718,33 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6089</v>
+        <v>0.5647</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-156</v>
-      </c>
-      <c r="H128" s="15" t="n"/>
+        <v>-130</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>170</v>
+      </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
         <v/>
@@ -18763,7 +18767,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18780,32 +18784,32 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5023</v>
+        <v>0.4539732</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-101</v>
+        <v>120</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18829,7 +18833,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18846,32 +18850,32 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4977</v>
+        <v>0.5460268</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>101</v>
+        <v>-120</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18895,7 +18899,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18912,32 +18916,32 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4</v>
+        <v>0.5434</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>150</v>
+        <v>-119</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18961,7 +18965,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18978,32 +18982,32 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ St. Louis Cardinals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.6</v>
+        <v>0.4566</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-150</v>
+        <v>119</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-170</v>
+        <v>100</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19027,7 +19031,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19044,31 +19048,33 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.4529</v>
+        <v>0.3616</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="H133" s="15" t="n"/>
+        <v>177</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>160</v>
+      </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
         <v/>
@@ -19091,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 36.2% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19108,31 +19114,33 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5471</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H134" s="15" t="n"/>
+        <v>-177</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>178</v>
+      </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
         <v/>
@@ -19155,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 63.8% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19172,12 +19180,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -19187,14 +19195,14 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.3911</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="H135" s="15" t="n"/>
       <c r="I135" s="13">
@@ -19219,7 +19227,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19236,12 +19244,12 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -19251,14 +19259,14 @@
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5389</v>
+        <v>0.6089</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-117</v>
+        <v>-156</v>
       </c>
       <c r="H136" s="15" t="n"/>
       <c r="I136" s="13">
@@ -19283,7 +19291,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19300,12 +19308,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -19319,13 +19327,13 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.511</v>
+        <v>0.5023</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -19349,7 +19357,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19366,12 +19374,12 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -19385,13 +19393,13 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.489</v>
+        <v>0.4977</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -19415,7 +19423,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19432,12 +19440,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -19447,17 +19455,17 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants -1.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.3995</v>
+        <v>0.4613</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -19481,7 +19489,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19498,12 +19506,12 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Atlanta Braves @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -19513,17 +19521,17 @@
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.6005</v>
+        <v>0.5387</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-150</v>
+        <v>-117</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>-145</v>
+        <v>170</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -19547,7 +19555,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19564,12 +19572,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -19579,14 +19587,14 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.3885</v>
+        <v>0.4529</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="H141" s="15" t="n"/>
       <c r="I141" s="13">
@@ -19611,7 +19619,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19628,12 +19636,12 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
@@ -19643,14 +19651,14 @@
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.6115</v>
+        <v>0.5471</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-157</v>
+        <v>-121</v>
       </c>
       <c r="H142" s="15" t="n"/>
       <c r="I142" s="13">
@@ -19675,7 +19683,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -157). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19692,12 +19700,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Colorado Rockies @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -19707,14 +19715,14 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.4619</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>-114</v>
+        <v>116</v>
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
@@ -19739,7 +19747,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19756,12 +19764,12 @@
       </c>
       <c r="B144" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Colorado Rockies @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -19771,14 +19779,14 @@
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.5381</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>114</v>
+        <v>-116</v>
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
@@ -19803,7 +19811,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19820,7 +19828,7 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -19830,23 +19838,21 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.3885</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="H145" s="15" t="n">
-        <v>104</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="H145" s="15" t="n"/>
       <c r="I145" s="13">
         <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
         <v/>
@@ -19869,7 +19875,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19886,7 +19892,7 @@
       </c>
       <c r="B146" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Diego Padres</t>
+          <t>Arizona Diamondbacks @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
@@ -19896,23 +19902,21 @@
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E146" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.6115</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H146" s="15" t="n">
-        <v>100</v>
-      </c>
+        <v>-157</v>
+      </c>
+      <c r="H146" s="15" t="n"/>
       <c r="I146" s="13">
         <f>IF($H$146="","",IF($H$146&lt;0,-$H$146/(-$H$146+100),100/($H$146+100)))</f>
         <v/>
@@ -19935,7 +19939,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 61.2% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19962,23 +19966,21 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.5966</v>
+        <v>0.5241</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>-148</v>
-      </c>
-      <c r="H147" s="15" t="n">
-        <v>-150</v>
-      </c>
+        <v>-110</v>
+      </c>
+      <c r="H147" s="15" t="n"/>
       <c r="I147" s="13">
         <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
         <v/>
@@ -20001,7 +20003,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20028,23 +20030,21 @@
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E148" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays -1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.4034</v>
+        <v>0.4759</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="H148" s="15" t="n">
-        <v>144</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="H148" s="15" t="n"/>
       <c r="I148" s="13">
         <f>IF($H$148="","",IF($H$148&lt;0,-$H$148/(-$H$148+100),100/($H$148+100)))</f>
         <v/>
@@ -20067,7 +20067,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20100,7 +20100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20640,12 +20640,14 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6054</v>
+        <v>0.67647</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-153</v>
-      </c>
-      <c r="H11" s="15" t="n"/>
+        <v>-209</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-120</v>
+      </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
         <v/>
@@ -20668,7 +20670,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 67.6% (fair -209). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -20704,12 +20706,14 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3946</v>
+        <v>0.32353</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>153</v>
-      </c>
-      <c r="H12" s="15" t="n"/>
+        <v>209</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>260</v>
+      </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
         <v/>
@@ -20732,7 +20736,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 32.4% (fair +209). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -20749,7 +20753,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -20759,21 +20763,23 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3563</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>181</v>
-      </c>
-      <c r="H13" s="15" t="n"/>
+        <v>-110</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
         <v/>
@@ -20796,7 +20802,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20813,7 +20819,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -20823,21 +20829,23 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6437</v>
+        <v>0.4752999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-181</v>
-      </c>
-      <c r="H14" s="15" t="n"/>
+        <v>110</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
         <v/>
@@ -20860,7 +20868,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20877,31 +20885,33 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Toronto Tempo +6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2121</v>
+        <v>0.5429</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>371</v>
-      </c>
-      <c r="H15" s="15" t="n"/>
+        <v>-119</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
         <v/>
@@ -20924,7 +20934,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 21.2% (fair +371). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -20941,31 +20951,33 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>New York Liberty -6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7879</v>
+        <v>0.4571</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-371</v>
-      </c>
-      <c r="H16" s="15" t="n"/>
+        <v>119</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
         <v/>
@@ -20988,7 +21000,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 78.8% (fair -371). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -21005,12 +21017,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -21020,16 +21032,18 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3925</v>
+        <v>0.4</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>155</v>
-      </c>
-      <c r="H17" s="15" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>170</v>
+      </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
         <v/>
@@ -21052,7 +21066,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -21069,12 +21083,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -21084,16 +21098,18 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6075</v>
+        <v>0.6</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H18" s="15" t="n"/>
+        <v>-150</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-115</v>
+      </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
         <v/>
@@ -21116,7 +21132,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -21125,9 +21141,1065 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Storm @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Over 178.5</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>178</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I19" s="13">
+        <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="16">
+        <f>IF($H$19="","",$F$19*IF($H$19&lt;0,-100/$H$19,$H$19/100)-(1-$F$19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>IF($H$19="","",MAX(0,($F$19*IF($H$19&lt;0,-100/$H$19,$H$19/100)-(1-$F$19))/IF($H$19&lt;0,-100/$H$19,$H$19/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L19" s="18">
+        <f>IF($H$19="","",ROUND(MIN($K$19,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M19" s="12">
+        <f>IF($J$19="","",IF($J$19&lt;0,"Pass",IF($J$19&lt;'Settings'!$B$4,"Thin",IF($J$19&lt;0.06,"✅ Sharp band",IF($J$19&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.0% (fair +178). Your call.</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="16">
+        <f>IF(OR($H$19="",$O$19=""),"",(1+IF($H$19&lt;0,-100/$H$19,$H$19/100))/(1+IF($O$19&lt;0,-100/$O$19,$O$19/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Storm @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Under 178.5</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.6404000000000001</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>-178</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I20" s="13">
+        <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IF($H$20="","",$F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>IF($H$20="","",MAX(0,($F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))/IF($H$20&lt;0,-100/$H$20,$H$20/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L20" s="18">
+        <f>IF($H$20="","",ROUND(MIN($K$20,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>IF($J$20="","",IF($J$20&lt;0,"Pass",IF($J$20&lt;'Settings'!$B$4,"Thin",IF($J$20&lt;0.06,"✅ Sharp band",IF($J$20&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.0% (fair -178). Your call.</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="16">
+        <f>IF(OR($H$20="",$O$20=""),"",(1+IF($H$20&lt;0,-100/$H$20,$H$20/100))/(1+IF($O$20&lt;0,-100/$O$20,$O$20/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Storm @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Washington Mystics -4.5</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I21" s="13">
+        <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="16">
+        <f>IF($H$21="","",$F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>IF($H$21="","",MAX(0,($F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))/IF($H$21&lt;0,-100/$H$21,$H$21/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L21" s="18">
+        <f>IF($H$21="","",ROUND(MIN($K$21,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IF($J$21="","",IF($J$21&lt;0,"Pass",IF($J$21&lt;'Settings'!$B$4,"Thin",IF($J$21&lt;0.06,"✅ Sharp band",IF($J$21&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.3% (fair -105). Your call.</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="16">
+        <f>IF(OR($H$21="",$O$21=""),"",(1+IF($H$21&lt;0,-100/$H$21,$H$21/100))/(1+IF($O$21&lt;0,-100/$O$21,$O$21/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Storm @ Washington Mystics</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Storm +4.5</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>112</v>
+      </c>
+      <c r="I22" s="13">
+        <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="16">
+        <f>IF($H$22="","",$F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF($H$22="","",MAX(0,($F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))/IF($H$22&lt;0,-100/$H$22,$H$22/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L22" s="18">
+        <f>IF($H$22="","",ROUND(MIN($K$22,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF($J$22="","",IF($J$22&lt;0,"Pass",IF($J$22&lt;'Settings'!$B$4,"Thin",IF($J$22&lt;0.06,"✅ Sharp band",IF($J$22&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.7% (fair +105). Your call.</t>
+        </is>
+      </c>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="16">
+        <f>IF(OR($H$22="",$O$22=""),"",(1+IF($H$22&lt;0,-100/$H$22,$H$22/100))/(1+IF($O$22&lt;0,-100/$O$22,$O$22/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.2190888999999999</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>356</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 21.9% (fair +356). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.7809111000000001</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>-356</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 78.1% (fair -356). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Over 176.5</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.5432</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.3% (fair -119). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Under 176.5</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.7% (fair +119). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Dallas Wings -9.5</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.8% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Sky @ Dallas Wings</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Sky +9.5</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.4923999999999999</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.2% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>163</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.0% (fair +150). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>-150</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-138</v>
+      </c>
+      <c r="I30" s="13">
+        <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>IF($H$30="","",$F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="17">
+        <f>IF($H$30="","",MAX(0,($F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))/IF($H$30&lt;0,-100/$H$30,$H$30/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L30" s="18">
+        <f>IF($H$30="","",ROUND(MIN($K$30,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M30" s="12">
+        <f>IF($J$30="","",IF($J$30&lt;0,"Pass",IF($J$30&lt;'Settings'!$B$4,"Thin",IF($J$30&lt;0.06,"✅ Sharp band",IF($J$30&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.0% (fair -150). Your call.</t>
+        </is>
+      </c>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="16">
+        <f>IF(OR($H$30="",$O$30=""),"",(1+IF($H$30&lt;0,-100/$H$30,$H$30/100))/(1+IF($O$30&lt;0,-100/$O$30,$O$30/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Over 180</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-118</v>
+      </c>
+      <c r="I31" s="13">
+        <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="16">
+        <f>IF($H$31="","",$F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>IF($H$31="","",MAX(0,($F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))/IF($H$31&lt;0,-100/$H$31,$H$31/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L31" s="18">
+        <f>IF($H$31="","",ROUND(MIN($K$31,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>IF($J$31="","",IF($J$31&lt;0,"Pass",IF($J$31&lt;'Settings'!$B$4,"Thin",IF($J$31&lt;0.06,"✅ Sharp band",IF($J$31&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.8% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="16">
+        <f>IF(OR($H$31="",$O$31=""),"",(1+IF($H$31&lt;0,-100/$H$31,$H$31/100))/(1+IF($O$31&lt;0,-100/$O$31,$O$31/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Under 180</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-118</v>
+      </c>
+      <c r="I32" s="13">
+        <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>IF($H$32="","",$F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="17">
+        <f>IF($H$32="","",MAX(0,($F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))/IF($H$32&lt;0,-100/$H$32,$H$32/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L32" s="18">
+        <f>IF($H$32="","",ROUND(MIN($K$32,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M32" s="12">
+        <f>IF($J$32="","",IF($J$32&lt;0,"Pass",IF($J$32&lt;'Settings'!$B$4,"Thin",IF($J$32&lt;0.06,"✅ Sharp band",IF($J$32&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.0% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="16">
+        <f>IF(OR($H$32="",$O$32=""),"",(1+IF($H$32&lt;0,-100/$H$32,$H$32/100))/(1+IF($O$32&lt;0,-100/$O$32,$O$32/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces -3.5</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I33" s="13">
+        <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="16">
+        <f>IF($H$33="","",$F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>IF($H$33="","",MAX(0,($F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))/IF($H$33&lt;0,-100/$H$33,$H$33/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L33" s="18">
+        <f>IF($H$33="","",ROUND(MIN($K$33,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M33" s="12">
+        <f>IF($J$33="","",IF($J$33&lt;0,"Pass",IF($J$33&lt;'Settings'!$B$4,"Thin",IF($J$33&lt;0.06,"✅ Sharp band",IF($J$33&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.2% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="16">
+        <f>IF(OR($H$33="",$O$33=""),"",(1+IF($H$33&lt;0,-100/$H$33,$H$33/100))/(1+IF($O$33&lt;0,-100/$O$33,$O$33/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Indiana Fever @ Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>Indiana Fever +3.5</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.4975000000000001</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-114</v>
+      </c>
+      <c r="I34" s="13">
+        <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="16">
+        <f>IF($H$34="","",$F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="17">
+        <f>IF($H$34="","",MAX(0,($F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))/IF($H$34&lt;0,-100/$H$34,$H$34/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L34" s="18">
+        <f>IF($H$34="","",ROUND(MIN($K$34,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M34" s="12">
+        <f>IF($J$34="","",IF($J$34&lt;0,"Pass",IF($J$34&lt;'Settings'!$B$4,"Thin",IF($J$34&lt;0.06,"✅ Sharp band",IF($J$34&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.8% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="16">
+        <f>IF(OR($H$34="",$O$34=""),"",(1+IF($H$34&lt;0,-100/$H$34,$H$34/100))/(1+IF($O$34&lt;0,-100/$O$34,$O$34/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J18">
+  <conditionalFormatting sqref="J5:J34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -21231,28 +22303,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2494</v>
+        <v>0.2497</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4105</v>
+        <v>0.4084</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-54.56</v>
+        <v>-57.69</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-10.62</v>
+        <v>-11.01</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>4.41</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5333</v>
+        <v>0.5349</v>
       </c>
     </row>
     <row r="6">
@@ -21262,28 +22334,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2498</v>
+        <v>0.2502</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4079</v>
+        <v>0.4056</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-53.36</v>
+        <v>-56.49</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-11.7</v>
+        <v>-12.12</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5541</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="7">
@@ -21366,7 +22438,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=391, ECE 0.043 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=395, ECE 0.044 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -21461,16 +22533,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.4589</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4309</v>
+        <v>0.432</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.028</v>
+        <v>-0.0269</v>
       </c>
     </row>
     <row r="21">
@@ -21480,16 +22552,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.543</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5417</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>0.0019</v>
+        <v>-0.0013</v>
       </c>
     </row>
     <row r="22">
@@ -21499,16 +22571,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>0.6402</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.5778</v>
+        <v>0.5652</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.0625</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="23">
